--- a/docs/downloads/Burloak.xlsx
+++ b/docs/downloads/Burloak.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -457,17 +457,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Nasato</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jan.canada2005@gmail.com</t>
+          <t>nasatopeter13@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandi</t>
+          <t>Glenda</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Segato</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sandi@pickleplexclub.ca</t>
+          <t>glendamargaret@live.ca</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Laughlin</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lukelaughlin44@icloud.com</t>
+          <t>susan.gibson@rogers.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Jaleel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gooding</t>
+          <t>Paje</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>thecoachgooding@gmail.com</t>
+          <t>jaleel.paje@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tashya</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sison</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tashyacaleon@gmail.com</t>
+          <t>jan.canada2005@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sHENDOSH</t>
+          <t>Husnain</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MADHUSUDHAN</t>
+          <t>Sheikh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shendoshm@gmail.com</t>
+          <t>hasnains19@icloud.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Khoi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>Doan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dannyjose@me.com</t>
+          <t>hyokoon@yahoo.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,15 +611,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Spencer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sandi@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -629,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>MCTEAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nixon_greg@yahoo.ca</t>
+          <t>mctear@prothane.ca</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -651,15 +655,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cole</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chong</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Goldsack</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lggoldsack@gmail.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -669,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Choy</t>
+          <t>MCTEAR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jacob.choy@live.ca</t>
+          <t>sales@prothane.ca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -691,15 +699,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Muhammad Abdulla</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Irianto</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>Saif</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>m.abdullahsaif@hotmail.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -709,15 +721,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Abedeen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Remtulla</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>abedeen.remtulla@gmail.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -727,15 +743,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Irianto</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Gooding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>thecoachgooding@gmail.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -745,15 +765,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dez</t>
+          <t>Dorothy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lopez</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Renzi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dorothyrenzi@outlook.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -763,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Tashya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lopez</t>
+          <t>Sison</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jasonlopez53@hotmail.com</t>
+          <t>tashyacaleon@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -785,15 +809,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Yiyun</t>
+          <t>Karissa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Boughner</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>karissaboughner@gmail.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -803,15 +831,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Lishan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Taneza</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lishanc@yahoo.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -821,15 +853,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aashir</t>
+          <t>Jeannie</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Meeran</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jeanniesmith2000@rogers.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -839,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Rohra</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>liuyingalice@gmail.com</t>
+          <t>rohan_rohra@yahoo.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -861,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scott David</t>
+          <t>Aahil</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Worden</t>
+          <t>Charania</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sworden@multimatic.com</t>
+          <t>aahil98@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -883,15 +919,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manny</t>
+          <t>sHENDOSH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Virtudazo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>MADHUSUDHAN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>shendoshm@gmail.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -901,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Burford</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>markch58@gmail.com</t>
+          <t>dannyjose@me.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -923,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lynne</t>
+          <t>Julianna</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maksuta</t>
+          <t>Guglietti</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>lsharp2@cogeco.ca</t>
+          <t>jguglietti@melroseinvestments.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -945,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Muise</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>amandamariejoyce@gmail.com</t>
+          <t>dougmuise55@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -967,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dat</t>
+          <t>RENEE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pham</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>datpham.ca@gmail.com</t>
+          <t>rphillips@melroseinvestments.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -989,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cherio</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>My</t>
+          <t>Plener</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cherio.my@gmail.com</t>
+          <t>thepleners@rogers.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1011,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ilona</t>
+          <t>Cyndi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Judeikiene</t>
+          <t>Boado</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ilona0311@gmail.com</t>
+          <t>bcyndi92@gmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1033,12 +1073,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cam</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lu</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1051,15 +1091,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marchetti</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Nixon</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nixon_greg@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1069,19 +1113,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>cole</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Han</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>hano72821@gmail.com</t>
-        </is>
-      </c>
+          <t>Chong</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1091,17 +1131,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rafat</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abu-Zeineh</t>
+          <t>Choy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rafat.abuzeineh@gmail.com</t>
+          <t>jacob.choy@live.ca</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1113,19 +1153,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Trizzia</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Delfin</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>trizziadelfin@gmail.com</t>
-        </is>
-      </c>
+          <t>Irianto</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1135,19 +1171,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vit</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>annevit.av@icloud.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1157,12 +1189,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Uyen</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diep</t>
+          <t>Irianto</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1175,19 +1207,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Dez</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quinsay</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>r.quinsay@gmail.com</t>
-        </is>
-      </c>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1197,17 +1225,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Yong</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Lopez</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jiangyong1998@hotmail.com</t>
+          <t>jasonlopez53@hotmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1219,12 +1247,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Maliyah</t>
+          <t>Yiyun</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jeshani</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1237,19 +1265,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Xin</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deng</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>cindydeng322@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1259,19 +1283,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jeanette</t>
+          <t>Aashir</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Perez</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>jeanetteperez72@gmail.com</t>
-        </is>
-      </c>
+          <t>Meeran</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1281,15 +1301,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Saad</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>liuyingalice@gmail.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1299,17 +1323,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bibi</t>
+          <t>Scott David</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Popovic</t>
+          <t>Worden</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>biba018@rogers.com</t>
+          <t>sworden@multimatic.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1321,19 +1345,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Haidan</t>
+          <t>Manny</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>haiden_wang@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Virtudazo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1343,15 +1363,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hu</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Burford</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>markch58@gmail.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1361,15 +1385,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Lynne</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rutter</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Maksuta</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>lsharp2@cogeco.ca</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1379,17 +1407,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>deanna</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>badovinac</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dbadovinac@fibercast.com</t>
+          <t>amandamariejoyce@gmail.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1401,17 +1429,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vucic</t>
+          <t>Henley</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kathy@parass.com</t>
+          <t>luke@pickleplex.ca</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1423,17 +1451,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Dat</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Eccles</t>
+          <t>Pham</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>stevieex@gmail.com</t>
+          <t>datpham.ca@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1445,17 +1473,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Cherio</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>My</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>brucehankmoore@gmail.com</t>
+          <t>cherio.my@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1467,17 +1495,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ilona</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gilligan</t>
+          <t>Judeikiene</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>kevin6862@hotmail.com</t>
+          <t>ilona0311@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1489,19 +1517,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>cam</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kelly</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>mary.kelly.remax@gmail.com</t>
-        </is>
-      </c>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1511,15 +1535,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rose</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Elvin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>robertelvin1@gmail.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1529,19 +1557,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kvesic</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>knezic_zeljka@yahoo.com</t>
-        </is>
-      </c>
+          <t>Marchetti</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1551,17 +1575,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>steve</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kelly</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>steve.wayne.kelly@gmail.com</t>
+          <t>hano72821@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1573,15 +1597,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Baraa</t>
+          <t>Rafat</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Abu-Zeineh</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>rafat.abuzeineh@gmail.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1591,15 +1619,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Trizzia</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Samuels</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>trizziadelfin@gmail.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1609,15 +1641,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nataly</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Vit</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>annevit.av@icloud.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1627,12 +1663,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Uyen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Diep</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1645,17 +1681,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bantin</t>
+          <t>Quinsay</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>colincbantin@gmail.com</t>
+          <t>r.quinsay@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1667,15 +1703,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Yong</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Froats</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Jiang</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jiangyong1998@hotmail.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1685,19 +1725,15 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Maliyah</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Henderson</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>larrymhenderson@gmail.com</t>
-        </is>
-      </c>
+          <t>Jeshani</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1707,17 +1743,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Xin</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Modi</t>
+          <t>Deng</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>bonnie.modi@gmail.com</t>
+          <t>cindydeng322@gmail.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1729,15 +1765,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Jeanette</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ross</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Perez</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jeanetteperez72@gmail.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1747,12 +1787,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Elliot</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Whittington</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1765,15 +1805,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Bibi</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Popovic</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>biba018@rogers.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1783,15 +1827,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Haidan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>haiden_wang@hotmail.ca</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1801,12 +1849,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Velanoff</t>
+          <t>Hu</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1819,12 +1867,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Edlyn</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Rutter</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1837,17 +1885,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>deanna</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kijak</t>
+          <t>badovinac</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>petey.kijak@gmail.com</t>
+          <t>dbadovinac@fibercast.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1859,15 +1907,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sapra</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Vucic</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>kathy@parass.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1877,17 +1929,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ella Rose</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Eccles</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>rmakrma@gmail.com</t>
+          <t>stevieex@gmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1899,15 +1951,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jacqueline</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Moore</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>brucehankmoore@gmail.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1917,15 +1973,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>Gilligan</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kevin6862@hotmail.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1935,15 +1995,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Prendergast</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>mary.kelly.remax@gmail.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1953,12 +2017,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prendergast</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1971,15 +2035,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Oren</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lasko</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Kvesic</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>knezic_zeljka@yahoo.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1989,15 +2057,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Oshra</t>
+          <t>steve</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lasko</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>steve.wayne.kelly@gmail.com</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2007,19 +2079,15 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Baraa</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Flowers</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>jjflowers@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2029,19 +2097,15 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>antony</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>han</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>uw.antony@gmail.com</t>
-        </is>
-      </c>
+          <t>Samuels</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2051,12 +2115,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Nataly</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2069,12 +2133,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Haichen (Henry)</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2087,17 +2151,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Divya</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kwatra</t>
+          <t>Bantin</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>diiu@hotmail.com</t>
+          <t>colincbantin@gmail.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2109,19 +2173,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>McMillan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>jackmcmi17@gmail.com</t>
-        </is>
-      </c>
+          <t>Froats</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2131,17 +2191,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Costa</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>fabian.pagani@icloud.com</t>
+          <t>larrymhenderson@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2153,17 +2213,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Melody</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Modi</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>melody2250hotmail@hotmail.com</t>
+          <t>bonnie.modi@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2175,19 +2235,15 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>justin</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>bradt</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>justinbradt@gmail.com</t>
-        </is>
-      </c>
+          <t>Ross</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2197,12 +2253,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Elliot</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quach</t>
+          <t>Whittington</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2215,12 +2271,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Griffith</t>
+          <t>Von Zuben</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2233,19 +2289,15 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tanner</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>scrappiedoo10@hotmail.com</t>
-        </is>
-      </c>
+          <t>Von Zuben</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2255,12 +2307,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Velanoff</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2273,12 +2325,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Edlyn</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deir</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2291,17 +2343,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dhir</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kothari</t>
+          <t>Kijak</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mr.dhirkothari@gmail.com</t>
+          <t>petey.kijak@gmail.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2313,19 +2365,15 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>morgan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>brian.k.morgan@hotmail.com</t>
-        </is>
-      </c>
+          <t>Sapra</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2335,20 +2383,6804 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>Ella Rose</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>rmakrma@gmail.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Jacqueline</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Prendergast</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Prendergast</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Oren</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Lasko</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Oshra</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Lasko</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jjflowers@hotmail.ca</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>antony</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>han</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>uw.antony@gmail.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Antony</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Haichen (Henry)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Divya</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Kwatra</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>diiu@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jackmcmi17@gmail.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>fabian.pagani@icloud.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Melody</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>melody2250hotmail@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>justin</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>bradt</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>justinbradt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Danny</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Quach</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Gail</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Griffith</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Dantes</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>xanderdantes03@gmail.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Catherine</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>scrappiedoo10@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Nolan</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Riley</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deir</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Dhir</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Kothari</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>mr.dhirkothari@gmail.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>brian</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>morgan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>brian.k.morgan@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>Chad</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>cvbaker@hotmail.com</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Amy</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bobbitt</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>amy.bobbitt@ig.ca</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Arvind</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Kochar</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>pinto</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>leogbarone@icloud.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Al Sayed</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>emilyalsayed@gmail.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Royan</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Arhaan</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Jinnah</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Arham</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Jinnah</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Thomson</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>thomson_alice@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Hugo</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Maclean</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>hugomaclean55@gmail.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Hillmer</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deary-Yu</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Perevalova</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Hillmer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Barb</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pitt</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>barbpitt21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Eunice</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Dayrit</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>eunicereniel_d@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Eason</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Katrina</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>katwalker04@gmail.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jake</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>walker.cm.jake@gmail.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Gibbard</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>stevengibbard@gmail.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>aframe@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Lepore</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>lepore235@gmail.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>McNamara</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ryanmdirect@gmail.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Robinson</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>dave.krown@gmail.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Marshall</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jenmarshall887@gmail.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Craig</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Gagliano</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>lola.gagliano68@gmail.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Tracy</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>tracyhamilton@mail.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Steeds</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>julesdolby1979@gmail.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>matt</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>mckee</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>matthewmckee365@gmail.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ray</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>porter</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>nanporter@rogers.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Alissa</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Shields</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>alissas1177@gmail.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>victoria</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>leeco</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>torileeco@icloud.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Andrews</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>gregory.c.andrews@gmail.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Lawrence</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>iamredlaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Shields</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>dshields13177@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Ritesh</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Jagtiani</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>riteshjagtgiani@gmail.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Defrang</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>tina.defrang@gmail.com</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Yuan</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Fang</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>noodle_f@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Brydon</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ron@francishockey.com</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Rhea</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>rhea.bailey@utoronto.ca</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Aa</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>fapro36@gmail.com</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>aimeeporter20@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Anne</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>frameanne5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Nadinr</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Clarke</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>clarkey2424@icloud.com</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Kaczur</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>heather.kaczur@gmail.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Tronetti</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>jtronetti@genesiscri.com</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Micheal</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Plouffe</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>micheal.plouffe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Heidi</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Plouffe</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Aimee</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Mann</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>tmann1999@gmail.com</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Noelle</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sargeant</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>nsargeant427@gmaul.com</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>francishockeygroup@gmail.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Tam</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>jacky.tam@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Kathleen</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D'Sylva</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>kdsylva1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Vankessel</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>wendy.vankessel@me.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Lin</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Kranz</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>lin_kranz@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Keyana</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Segato</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>kfsegato@icloud.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>saeed</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>seyedan</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>saeed.s83@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ellen</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Kawamoto</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>e.kawamoto@live.ca</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sehr</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Bhatti</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sehrbhatti@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Zach</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pepetone</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>zp7120@gmail.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Kerkhof</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>jacobkerkhof@gmail.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Miao</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>jenny.miao@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Cudek</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ncudek@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Vivian</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Luu</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>viluu@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>melissa</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>thoma</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>methoma@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Charlize</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Cabayan</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>charlizecabayan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Ramy</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Mahfouz</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ramyrmahfouz@gmail.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Harianto</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>veepetal@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Lucy</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Gao</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>l27gao@uwaterloo.ca</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>gauravi</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Mehta</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>gauravim@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Rico</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>li.rico10123@gmail.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Hudson</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>thudson@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Seana</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Maennling</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>seanamaennling@icloud.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Dickson</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>patdickson1234@gmail.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ASMITA</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>WAGHMARE</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>aswaghmare@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Aamir</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Awan</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>connect.the.dotinc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>newjie@msn.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Shannon</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Clarke</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>shannahan@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Hugh</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>McCrie</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>hmccrie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Feng</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>fengzhangbb@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>frances</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>coakley</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>fcoakley@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Fisher</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>yu</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>fisheryu@thefishegroup.ca</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Iain</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Munro</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>iainmunro5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Ren</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>renxiaodie@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>paul.rogers@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Fukuchi</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>mark@fukuchi.ca</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Gillian</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>gilliangmayo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Peters</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>stephenpeters235@gmail.com</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Umang</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>umangsharma98@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Howard</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>reachkarahoward@gmail.com</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Gurinder</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>gurinder_tatle@live.ca</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Perrino</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>perrinoh@hdsb.ca</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Shaydon</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Leiba</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>shaydonleiba@gmail.com</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Manvir</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Sidhu</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>sidhu.manvir98@gmail.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sahib</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Kamoh</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>sahib2k7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Paige</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Mander</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>paigeeamander@gmail.com</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Vanessa</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Cockshutt</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>vanessacockshutt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>DANNY</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>AMARAL</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>danny_amaral@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Puneet</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Mand</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>p.smand@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Ajit</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Devasia</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ajit.devasia@gmail.com</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>WESLEY</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>RODRICKS</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>rodricks_wd@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Rajan</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Dhaliwal</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>rajansing_d@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Gulneet</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Mand</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>gulneetk.mand@gmail.com</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Bal</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Chahal</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>bella.chahal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Everett</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>neverett7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>katie</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>emery</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>katieemeryis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Pierre</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Olivier</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>pierrejolivier@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Daron</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>McGregor</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>dmcgregor@melroseinvestments.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Mikaal</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Ansari</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ansari.mikaal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Kramer</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>123fatcat36@gmail.com</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>davide</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>baldassarra</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>db@melroseinvestments.com</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Aylin</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Gurer</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>gurer.aylin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Aayan</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>bonilla</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>1bonillacaay@hdsb.ca</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>YIJIA</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>LIU</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>yijia01.liu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Dela Paz</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>lrdelapaz98@gmail.com</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Whitten</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>whittenjulia@gmail.com</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Barclay</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>jbarclay@abacom-tech.com</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Bianca</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Walton</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>biancacwalton@gmail.com</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Yune</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>jessyune@gmail.com</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ALEXANDRA</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>COLELLA</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>sunnygal@duck.com</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Donnelly</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>jdonnellybcba@gmail.com</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>AUBREE</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>FRANCIS</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>aubsfrancis10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Deng</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>bjdky951120@gmail.com</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>`april</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Tyminski</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>atyminski16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Yuzhou</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Jiang</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>jiangyuzhoufred@gmail.com</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Van Dinter</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>jeffandkatherine@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Brydon</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Fang</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Daren</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>hamza</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>alhaid</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>hamza.alhaid@gmail.com</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Aubree</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Osama</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Javed</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>osamajvd@gmail.com</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Marian</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Tiqui</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>mariantiqui@gmail.com</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Qinqin</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Hua</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>iris0628g1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Karin</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Nesbitt</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>nesbittkarin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Julien</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Pellicano</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>jpellicano@melroseinvestments.com</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>ian@safenames.ca</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Nadhim</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Kadhim</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>nadhimjawad@gmail.com</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Keli</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Burgess</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>keli.benner@gmail.com</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>saad</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>saadalee@gmail.com</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Anita</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Fabac</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>anitafabac50@gmail.com</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Karine</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Kaplan</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>karine@promotionalsource.ca</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Lorraine</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Hogan</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>thehoganfamily@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>aanderson@melroseinvestments.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Stefano</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Bomben</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>stefbomben@gmail.com</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Rene</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Quercia</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>rene.quercia@icloud.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>dgonzalez@melroseinvestments.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Barry</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Mee</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>mee.barry@gmail.com</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Markovski</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>gabemarko@gmail.com</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Damario</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>paul@dimario.ca</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Curtis</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>murray.curtis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Annie</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Barnshaw</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>anneebarnshaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Paolo</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Delutis</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>pdelutis@melroseinvestments.com</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Neale</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>rachel.richard.neale@gmail.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Tomisin</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Idowu</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>idomisin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Pope</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>kpope24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Musa</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Manzar</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>musamanzar7004@gmail.com</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Finley</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Spivak</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>spivaks@hdsb.ca</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Marian</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Heys</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>marianheys9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Rishi</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>rishipatel999@gmail.com</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Wilde</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>philipwilde@live.ca</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Susan</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>gracehypnosis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Padro</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Gutierrez</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>ptsbrg0@gmail.com</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Parul</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Vora</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>parulvora@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Taren</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>taren_singh@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Deb</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Couture</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>deb.couture2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Bev</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Nicholls</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>bnicholls@tieroneoss.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Barbeau</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>chrisbarbeau@icloud.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Spivak</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>srobertson8@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Naryan</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>naryanpatel9999@gmail.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Chandra</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Maracle</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>cfmaracle2@aol.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Xiaoling</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>xllbrown@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Taranjeet</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>taran_singh@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Naya</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>nayapatel999@gmail.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Ammar</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Shaarbaf</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>shaarbafammar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Weber</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>daveweber@outlook.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Ali A</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Shaarbaf</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>raid1shaarbaf@gmail.com</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Youssif</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Said</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>alaanialfred@gmail.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Donati</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>donatikatie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Chad</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Hinks</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>hinkster@gmail.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Van Bavel</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>kyle@vanbavel.ca</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Glenn</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>justin_glenn@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Sashi</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Bala</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>bsashi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Zaid</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Shaarbaf</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>raid.shaarbaf@bchs.sys.org</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Weber</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>dsloweber@gmail.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Shaaeaf</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>ali1shaarba@gmail.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Milutinovich</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>jotina99@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Rosanna</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Soh</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>rosannasoh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Cadogan</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>tcadogan1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Gina</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Acosta</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>gacosta104@hormail.com</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Tharani</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Balachandran</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>tharaniy28@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Shaarbaf</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>fatima.shaarbaf@gmail.com</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Benyo</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>steven.benyo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Alisha</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Van Bavel</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>alishavanbavel@gmail.com</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Joan</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Cooper</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>bjoancooper62@gmail.com</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Alajeely</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>hamzaalajeely08@gmail.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Shaarbaf</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>ali1shaarbaf@gmail.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Mustafa</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Rizvi</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>mustafa_rizvi@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>matthew</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>nesbitt</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>mnesbitt@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Dylan</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Nesbitt</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>nesbittdylan4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Joo-Meng</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Soh</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>joomsoh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>braeden</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Nesbitt</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>nesbittbraeden11@gmail.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Lamees</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Al Ethari</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>lalethari@gmail.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Rasha</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Salih</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>rasha1salih@gmail.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Grand</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Cheng</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>grandkcheng@gmail.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>pam</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>rogers</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>rogerspam412@gmail.com</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>21arm31@queensu.ca</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Alazar</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>alazarnoah@gmail.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Wozniak</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>kylewozniak1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Haraish</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Kuarsingh</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>haraish.kuarsingh@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Hop Hing</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>chris.hophing@gmail.com</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Radivojsa</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>matthew.radivjsa@gmail.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Gobbatto</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>julia.gobbatto@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Lou</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Smeyers</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>lou.smeyers@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Sawrantschuk</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>nick.sawrantschuk@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Ramy</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Akladios</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ramy_akladios@live.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Moldonado</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>famaldomado2001@gmail.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Sheryl Lynn</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>sheryllynnlane@gmail.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Jacqui</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Hop Hing</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>jacs.hh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Barb</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Hillis</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>barbhillis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Stanley</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>stanley.wang.king@gmail.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Usama</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>muhammad.usama@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>JEANNIE</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>jeanniesmith20002@rogers.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Cull</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>jefe2401@gmail.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Judy</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>judy.li@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Sandy</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Tung</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>tungsj68@gmail.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Oliver</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Tung</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>olivert1512@gmail.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Sherry</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Kerr</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>sherrykerr57@gmail.com</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>mike</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>hansford</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>mike@corbettssports.ca</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>christine</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>marshall</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>christine.marshall00@gmail.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>MARIE</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>D/SOUZA</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>mdsouza@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Ralp Michael</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Reusi</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>michael.ralp.reusi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>cutts</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>doddie8984@gmail.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Donna</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Helm-Doherty</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>donna.helmdoherty@gmail.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>jennifer</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>bodenham</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>jenbodenham@gmail.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Stoba</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>james.stoba@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>tess</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>driedger</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>tessdriedger@gmail.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Monalisa</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Nicolcioiu</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>monalisa.nicolcioiu@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Halcovitch</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>rachelhalcovitch@gmail.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Eddie</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>eddie_revcan@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>LAURA</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>DIMATTEO</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>dancers2mom@gmail.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>DONNA</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>GILLIES MARSON</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>gilliesmarson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Rosman</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>kimrosman27@gmail.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Janet</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Gillis</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>janet.gillis@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Kristofer</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Collins</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>kriscollins9@icloud.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Lynn</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Wu</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>lynn.x.wu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Alison</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>alisondouglas999@gmail.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Rosalind</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Clarke</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>clarker@mcmaster.ca</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>jasmine</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>rishi</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>jasmine.rishi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Crosbie</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>michael.crosbie@doane.gt.ca</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>NIKITA</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SETHI</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>sethinikita04@gmail.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>JANET</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>CARANCI</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>janetcaranci@gmail.com</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>SEAN</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>MURPHY</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>semurphy@deloitte.ca</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Gurdeep</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Ghatehorde</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>gurdeepg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Gurpreet</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Saran</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>saran9257@gmail.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Sanghera</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>sangherajoe1977@gmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Parm</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>parm76@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Correia</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>kevincorreia28@gmail.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Gurjeet</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>gurjeet.guram18@gmail.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Hyslop</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>markhyslop6@gmail.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Awwad</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>yawwad11@aucegypt.edu</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Vandenbarselaar</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>jack.vandenbarselaar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Elsheikh</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>sara.sameh.elsheikh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Marina</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Galchinska</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>marina_galchinska@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Patti</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>pkent44@gmail.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Le</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>ncyl2002@gmail.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>alexandergibby2000@gmail.com</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Mu</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>admaila@gmail.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Stacey</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Hurley</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>sleehurley@gmail.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Colette</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>colettedublin5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Siok Wong(Emily)</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>emilysk18@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Sania</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Bains</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>saniabains48@gmail.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Qianying</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>tang5241@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Carl</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Franic</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>c_franic@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Yin</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>tongca@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>jteallen17@gmail.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Esteban</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Pacheco</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>estebanpachesantana@gmail.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Stu</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Ross</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>stuart.jamesross4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Eby</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Os</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>osime.eby@gmail.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Mouneer</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Mohamad</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>mouneer.m6@gmail.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Brodie</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Dionne</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>brodiedmd@icloud.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Rakesh</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Gupta</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>rgupta23@gmail.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Rene</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Quercia</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Lo</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>lilylii576726@outlook.com</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Dionne</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>ryandionne31@gmail.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Saleh</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>oezzatsaleh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Will</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>wevans1711@gmail.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Burloak.xlsx
+++ b/docs/downloads/Burloak.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -457,17 +457,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Johnathan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jan.canada2005@gmail.com</t>
+          <t>js10.pickleball@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandi</t>
+          <t>mike</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>moll</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sandi@pickleplexclub.ca</t>
+          <t>mike@mikemoll.co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Goldsack</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lggoldsack@gmail.com</t>
+          <t>jan.canada2005@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCTEAR</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sales@prothane.ca</t>
+          <t>sandi@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Shayaan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gooding</t>
+          <t>Alibhai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thecoachgooding@gmail.com</t>
+          <t>shayaan.alibhai@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tashya</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sison</t>
+          <t>Goldsack</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tashyacaleon@gmail.com</t>
+          <t>lggoldsack@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sHENDOSH</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MADHUSUDHAN</t>
+          <t>MCTEAR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>shendoshm@gmail.com</t>
+          <t>sales@prothane.ca</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>Gooding</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dannyjose@me.com</t>
+          <t>thecoachgooding@gmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,15 +633,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Imtiaz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Alibhai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>imtiaz.alibhai@gmail.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -651,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Tashya</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>Sison</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nixon_greg@yahoo.ca</t>
+          <t>tashyacaleon@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -673,15 +677,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cole</t>
+          <t>sHENDOSH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chong</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>MADHUSUDHAN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>shendoshm@gmail.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -691,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Choy</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jacob.choy@live.ca</t>
+          <t>dannyjose@me.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -713,15 +721,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Irianto</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Chant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>chant.j09@gmail.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -731,12 +743,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -749,15 +761,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Irianto</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Nixon</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nixon_greg@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -767,12 +783,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dez</t>
+          <t>cole</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lopez</t>
+          <t>Chong</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -785,17 +801,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lopez</t>
+          <t>Choy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jasonlopez53@hotmail.com</t>
+          <t>jacob.choy@live.ca</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -807,12 +823,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Yiyun</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Irianto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -825,7 +841,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -843,12 +859,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aashir</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Meeran</t>
+          <t>Irianto</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -861,19 +877,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Dez</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liu</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>liuyingalice@gmail.com</t>
-        </is>
-      </c>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -883,17 +895,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scott David</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worden</t>
+          <t>Lopez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sworden@multimatic.com</t>
+          <t>jasonlopez53@hotmail.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -905,12 +917,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Manny</t>
+          <t>Yiyun</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Virtudazo</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -923,19 +935,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Burford</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>markch58@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -945,19 +953,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lynne</t>
+          <t>Aashir</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maksuta</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>lsharp2@cogeco.ca</t>
-        </is>
-      </c>
+          <t>Meeran</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -967,17 +971,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>amandamariejoyce@gmail.com</t>
+          <t>liuyingalice@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -989,17 +993,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dat</t>
+          <t>Scott David</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pham</t>
+          <t>Worden</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>datpham.ca@gmail.com</t>
+          <t>sworden@multimatic.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1011,19 +1015,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cherio</t>
+          <t>Manny</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>My</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>cherio.my@gmail.com</t>
-        </is>
-      </c>
+          <t>Virtudazo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1033,17 +1033,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ilona</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Judeikiene</t>
+          <t>Burford</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ilona0311@gmail.com</t>
+          <t>markch58@gmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1055,15 +1055,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cam</t>
+          <t>Lynne</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Maksuta</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lsharp2@cogeco.ca</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1073,15 +1077,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marchetti</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>amandamariejoyce@gmail.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1091,17 +1099,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rafat</t>
+          <t>Dat</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abu-Zeineh</t>
+          <t>Pham</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rafat.abuzeineh@gmail.com</t>
+          <t>datpham.ca@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1113,17 +1121,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Trizzia</t>
+          <t>Cherio</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>My</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>trizziadelfin@gmail.com</t>
+          <t>cherio.my@gmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1135,17 +1143,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Ilona</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vit</t>
+          <t>Judeikiene</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>annevit.av@icloud.com</t>
+          <t>ilona0311@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1157,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Uyen</t>
+          <t>cam</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diep</t>
+          <t>lu</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1175,19 +1183,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Han</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ryanhan821@yahoo.com</t>
-        </is>
-      </c>
+          <t>Marchetti</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1197,17 +1201,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Rafat</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quinsay</t>
+          <t>Abu-Zeineh</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>r.quinsay@gmail.com</t>
+          <t>rafat.abuzeineh@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1219,17 +1223,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Yong</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Vit</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jiangyong1998@hotmail.com</t>
+          <t>annevit.av@icloud.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1241,12 +1245,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Maliyah</t>
+          <t>Uyen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jeshani</t>
+          <t>Diep</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1259,17 +1263,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Xin</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deng</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cindydeng322@gmail.com</t>
+          <t>ryanhan821@yahoo.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1281,17 +1285,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jeanette</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Perez</t>
+          <t>Quinsay</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jeanetteperez72@gmail.com</t>
+          <t>r.quinsay@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1303,15 +1307,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Yong</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saad</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Jiang</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jiangyong1998@hotmail.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1321,19 +1329,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bibi</t>
+          <t>Maliyah</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Popovic</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>biba018@rogers.com</t>
-        </is>
-      </c>
+          <t>Jeshani</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1343,17 +1347,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Haidan</t>
+          <t>Xin</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Deng</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>haiden_wang@hotmail.ca</t>
+          <t>cindydeng322@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1365,15 +1369,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Jeanette</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hu</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Perez</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jeanetteperez72@gmail.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1383,12 +1391,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rutter</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1401,17 +1409,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>deanna</t>
+          <t>Bibi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>badovinac</t>
+          <t>Popovic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dbadovinac@fibercast.com</t>
+          <t>biba018@rogers.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1423,17 +1431,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Haidan</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vucic</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kathy@parass.com</t>
+          <t>haiden_wang@hotmail.ca</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1445,19 +1453,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Moore</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>brucehankmoore@gmail.com</t>
-        </is>
-      </c>
+          <t>Hu</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1467,19 +1471,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gilligan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>kevin6862@hotmail.com</t>
-        </is>
-      </c>
+          <t>Rutter</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1489,17 +1489,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>deanna</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>badovinac</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mary.kelly.remax@gmail.com</t>
+          <t>dbadovinac@fibercast.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1511,15 +1511,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rose</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Vucic</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kathy@parass.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1529,17 +1533,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kvesic</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>knezic_zeljka@yahoo.com</t>
+          <t>brucehankmoore@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1551,17 +1555,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>steve</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kelly</t>
+          <t>Gilligan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>steve.wayne.kelly@gmail.com</t>
+          <t>kevin6862@hotmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1573,15 +1577,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Baraa</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mary.kelly.remax@gmail.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1591,12 +1599,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Samuels</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1609,15 +1617,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nataly</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Kvesic</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>knezic_zeljka@yahoo.com</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1627,15 +1639,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>steve</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>steve.wayne.kelly@gmail.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1645,19 +1661,15 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Baraa</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bantin</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>colincbantin@gmail.com</t>
-        </is>
-      </c>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1667,12 +1679,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Froats</t>
+          <t>Samuels</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1685,19 +1697,15 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Nataly</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Henderson</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>larrymhenderson@gmail.com</t>
-        </is>
-      </c>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1707,19 +1715,15 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Modi</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>bonnie.modi@gmail.com</t>
-        </is>
-      </c>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1729,15 +1733,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ross</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Bantin</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>colincbantin@gmail.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1747,12 +1755,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Elliot</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Whittington</t>
+          <t>Froats</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1765,15 +1773,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>larrymhenderson@gmail.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1783,15 +1795,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Modi</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>bonnie.modi@gmail.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1801,12 +1817,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Velanoff</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1819,12 +1835,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Edlyn</t>
+          <t>Elliot</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Whittington</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1837,19 +1853,15 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kijak</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>petey.kijak@gmail.com</t>
-        </is>
-      </c>
+          <t>Von Zuben</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1859,12 +1871,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sapra</t>
+          <t>Von Zuben</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1877,19 +1889,15 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ella Rose</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>rmakrma@gmail.com</t>
-        </is>
-      </c>
+          <t>Velanoff</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1899,12 +1907,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jacqueline</t>
+          <t>Edlyn</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1917,15 +1925,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>Kijak</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>petey.kijak@gmail.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1935,12 +1947,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Prendergast</t>
+          <t>Sapra</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1953,15 +1965,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Ella Rose</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prendergast</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>rmakrma@gmail.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1971,12 +1987,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Oren</t>
+          <t>Jacqueline</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lasko</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1989,12 +2005,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Oshra</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lasko</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2007,19 +2023,15 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Flowers</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>jjflowers@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Prendergast</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2029,19 +2041,15 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>antony</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>han</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>uw.antony@gmail.com</t>
-        </is>
-      </c>
+          <t>Prendergast</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2051,12 +2059,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Oren</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Lasko</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2069,12 +2077,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Haichen (Henry)</t>
+          <t>Oshra</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Lasko</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2087,17 +2095,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Divya</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kwatra</t>
+          <t>Flowers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>diiu@hotmail.com</t>
+          <t>jjflowers@hotmail.ca</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2109,17 +2117,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>antony</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>McMillan</t>
+          <t>han</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jackmcmi17@gmail.com</t>
+          <t>uw.antony@gmail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2131,19 +2139,15 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Costa</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>fabian.pagani@icloud.com</t>
-        </is>
-      </c>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2153,19 +2157,15 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Melody</t>
+          <t>Haichen (Henry)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>melody2250hotmail@hotmail.com</t>
-        </is>
-      </c>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2175,17 +2175,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>justin</t>
+          <t>Divya</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>bradt</t>
+          <t>Kwatra</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>justinbradt@gmail.com</t>
+          <t>diiu@hotmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2197,15 +2197,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quach</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>McMillan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>jackmcmi17@gmail.com</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2215,15 +2219,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Griffith</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>fabian.pagani@icloud.com</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2233,17 +2241,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Melody</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Cao</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>scrappiedoo10@hotmail.com</t>
+          <t>melody2250hotmail@hotmail.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2255,15 +2263,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>justin</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Han</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>bradt</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>justinbradt@gmail.com</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2273,12 +2285,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deir</t>
+          <t>Quach</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2291,19 +2303,15 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dhir</t>
+          <t>Gail</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kothari</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>mr.dhirkothari@gmail.com</t>
-        </is>
-      </c>
+          <t>Griffith</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2313,17 +2321,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>morgan</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>brian.k.morgan@hotmail.com</t>
+          <t>scrappiedoo10@hotmail.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2335,19 +2343,15 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>cvbaker@hotmail.com</t>
-        </is>
-      </c>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2357,19 +2361,15 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bobbitt</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>amy.bobbitt@ig.ca</t>
-        </is>
-      </c>
+          <t>Deir</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2379,15 +2379,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Arvind</t>
+          <t>Dhir</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kochar</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>Kothari</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>mr.dhirkothari@gmail.com</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2397,17 +2401,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>pinto</t>
+          <t>morgan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>leogbarone@icloud.com</t>
+          <t>brian.k.morgan@hotmail.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2419,15 +2423,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Royan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>cvbaker@hotmail.com</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2437,15 +2445,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Arhaan</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jinnah</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>Bobbitt</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>amy.bobbitt@ig.ca</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2455,12 +2467,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Arham</t>
+          <t>Arvind</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jinnah</t>
+          <t>Kochar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2473,15 +2485,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hillmer</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>pinto</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>leogbarone@icloud.com</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2491,12 +2507,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deary-Yu</t>
+          <t>Royan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2509,12 +2525,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Arhaan</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Perevalova</t>
+          <t>Jinnah</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2527,12 +2543,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Arham</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hillmer</t>
+          <t>Jinnah</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2545,19 +2561,15 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pitt</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>barbpitt21@gmail.com</t>
-        </is>
-      </c>
+          <t>Hillmer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2567,19 +2579,15 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Eunice</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dayrit</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>eunicereniel_d@yahoo.com</t>
-        </is>
-      </c>
+          <t>Deary-Yu</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2589,12 +2597,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Eason</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Perevalova</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2607,19 +2615,15 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Walker</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>katwalker04@gmail.com</t>
-        </is>
-      </c>
+          <t>Hillmer</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2629,17 +2633,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Pitt</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>walker.cm.jake@gmail.com</t>
+          <t>barbpitt21@gmail.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2651,15 +2655,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hamilton</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>Defrang</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>rolanddefrang@icloud.com</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2669,15 +2677,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Heidi</t>
+          <t>Eunice</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Plouffe</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>Dayrit</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>eunicereniel_d@yahoo.com</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2687,12 +2699,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Aimee</t>
+          <t>Eason</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Porter</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2705,17 +2717,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Keyana</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Segato</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>kfsegato@icloud.com</t>
+          <t>katwalker04@gmail.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2727,17 +2739,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Seana</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Maennling</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>seanamaennling@icloud.com</t>
+          <t>walker.cm.jake@gmail.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2749,19 +2761,15 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>gregc@pickleplex.ca</t>
-        </is>
-      </c>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2771,19 +2779,15 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mikaal</t>
+          <t>Heidi</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ansari</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>ansari.mikaal@gmail.com</t>
-        </is>
-      </c>
+          <t>Plouffe</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2793,19 +2797,15 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Aayan</t>
+          <t>Aimee</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>bonilla</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>1bonillacaay@hdsb.ca</t>
-        </is>
-      </c>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2815,15 +2815,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Keyana</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Segato</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>kfsegato@icloud.com</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2833,17 +2837,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Seana</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Donnelly</t>
+          <t>Maennling</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jdonnellybcba@gmail.com</t>
+          <t>seanamaennling@icloud.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2855,17 +2859,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AUBREE</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FRANCIS</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>aubsfrancis10@gmail.com</t>
+          <t>gregc@pickleplex.ca</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2877,15 +2881,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Brydon</t>
+          <t>Mikaal</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>Ansari</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ansari.mikaal@gmail.com</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2895,15 +2903,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Fang</t>
+          <t>Aayan</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>bonilla</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1bonillacaay@hdsb.ca</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2913,12 +2925,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Eddie</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2931,15 +2943,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Daren</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>Donnelly</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jdonnellybcba@gmail.com</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2949,15 +2965,19 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Aubree</t>
+          <t>AUBREE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>FRANCIS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>aubsfrancis10@gmail.com</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2967,19 +2987,15 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Stefano</t>
+          <t>Brydon</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bomben</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>stefbomben@gmail.com</t>
-        </is>
-      </c>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2989,19 +3005,15 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>matthew</t>
+          <t>Fang</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>nesbitt</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>mnesbitt@cogeco.ca</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3011,19 +3023,15 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Parm</t>
+          <t>Eddie</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>parm76@hotmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3033,19 +3041,15 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NOURA</t>
+          <t>Daren</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BALBAA</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>balbaanoura@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3055,12 +3059,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Rene</t>
+          <t>Aubree</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Quercia</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3073,17 +3077,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Stefano</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>McGuire</t>
+          <t>Bomben</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>mcguire11170@gmail.com</t>
+          <t>stefbomben@gmail.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3095,20 +3099,1680 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>matthew</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>nesbitt</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>mnesbitt@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Parm</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>parm76@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Bartlett</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jdbartlett@gmail.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>NOURA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BALBAA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>balbaanoura@gmail.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Rene</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Quercia</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>McGuire</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>mcguire11170@gmail.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t>jessica</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>rickus</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>jess.rickus@gmail.com</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>riccimatthew95@gmail.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Moazzam</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>zara.moazzam.16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Lindsay</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Hooper</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>lindsayhooper79@gmail.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CHANDRE</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MACDOUGALL</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>chandre@gmail.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Marina</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Magagna</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>marina45@rogers.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Lynda</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>robandlyndawilson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Berfelz</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bencoe01@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Alpaugh</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>tlalpaugh@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Snowden</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sydney.2205.ss@icloud.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Juzar</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ebrahimjee</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>juzzii@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Burgess</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>mike_burgess78@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ping</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lu</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>pinglu224@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Shannon</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Martins</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>smartins2@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Theresa</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Zamora</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>theresazam1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Yingmai</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Guo</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>guoyingmai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Brandon Scott</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Chow</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>O'Loughlin</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>linda_olo@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Gerry</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Tessier</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>tessiergerry@gmail.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>De Lucia</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>steve.delucia@ouitlook.com</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>nick</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>quartarone</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>nickquartarone04@gmail.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Deliah</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>McLane</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>deliah.custodio@icloud.com</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Qianying</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sadi</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Arbid</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>arbid.arbid@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Jin</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>xin_jin@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Harsh</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Gandhi</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>harsh.canada2018@gmail.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>tiger.liuy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jinhee</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>kinikini0429@gmail.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>RAIKO</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>raikolee@gmail.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Lico</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>jacobjlico@outlook.com</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>nathalie</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>devault-arbid</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>devault.devault@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Alison</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>alimiller314@gmail.com</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Xie</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>cynthia.xie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Titei</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>temp.100@live.com</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Yu</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Zhou</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>tinarainbox@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Marchese</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>marchese.ash@gmail.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Zamzam</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>omarrzamzam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Yena</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ynhk1127@gmail.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Montalbano</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>amontalbano75@gmail.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>luke.d.everest@gmail.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Nathan</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Tse</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>nathantse@live.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Farid</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>aawad62@gmail.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ethancox1337@gmail.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Akl</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>mohamedakl99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ron</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>borbas</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ronborbas@gmail.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>katelyn</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>chung</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>katelynchung99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Zhou</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>wangkejuan@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Oana</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Titei</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>oana@titei.com</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Hyravy</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>nikkihyravy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>jason</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>dennis</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>jasonbear34@live.ca</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>jerry</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>jerry.hm@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Roger</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Guillemette</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>rogerguillemette@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>bq</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>xu</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>mr.bq.xu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>janet</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>gallucci</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>j_delcol@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Hayden</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>mh@intersurgical.ca</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Montalbano</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>linda@graffretail.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>matheus</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>krumme</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>mjkrumme@gmail.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Vicky</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Zhou</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>wangkejuan+@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>alexander</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>chung</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>alexanderchung88@gmail.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>jamekoch9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>shuang</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>yao</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>stevenyaomolins@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Sherif</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Shama</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sherifshama@me.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>El</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>amahalwy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Compas</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>joshcompas@outlook.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>donna</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>petrarca</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>julesmom@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Elaine</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Boal</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>eboal@bell.net</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Gasparik</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>tgasparik@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Hu</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>claudia.nrsg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Lo</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>justinhllo10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Vander Velden</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>stewvelden@gmail.com</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>mohfouad01@gmail.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Burloak.xlsx
+++ b/docs/downloads/Burloak.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3121,17 +3121,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Parm</t>
+          <t>tania</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>tani</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>parm76@hotmail.com</t>
+          <t>ttani066@gmail.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3143,17 +3143,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Parm</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Bartlett</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jdbartlett@gmail.com</t>
+          <t>parm76@hotmail.com</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3165,17 +3165,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NOURA</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BALBAA</t>
+          <t>Bartlett</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>balbaanoura@gmail.com</t>
+          <t>jdbartlett@gmail.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3187,15 +3187,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Rene</t>
+          <t>NOURA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Quercia</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>BALBAA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>balbaanoura@gmail.com</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3205,19 +3209,15 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Rene</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>McGuire</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>mcguire11170@gmail.com</t>
-        </is>
-      </c>
+          <t>Quercia</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3227,17 +3227,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>jessica</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>rickus</t>
+          <t>McGuire</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jess.rickus@gmail.com</t>
+          <t>mcguire11170@gmail.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3249,17 +3249,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>jessica</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>rickus</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>riccimatthew95@gmail.com</t>
+          <t>jess.rickus@gmail.com</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3271,17 +3271,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Moazzam</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>zara.moazzam.16@gmail.com</t>
+          <t>riccimatthew95@gmail.com</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3293,17 +3293,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lindsay</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Hooper</t>
+          <t>Moazzam</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>lindsayhooper79@gmail.com</t>
+          <t>zara.moazzam.16@gmail.com</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3315,17 +3315,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CHANDRE</t>
+          <t>Lindsay</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MACDOUGALL</t>
+          <t>Hooper</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>chandre@gmail.com</t>
+          <t>lindsayhooper79@gmail.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3337,17 +3337,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>CHANDRE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Magagna</t>
+          <t>MACDOUGALL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>marina45@rogers.com</t>
+          <t>chandre@gmail.com</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3359,17 +3359,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Lynda</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Magagna</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>robandlyndawilson@gmail.com</t>
+          <t>marina45@rogers.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3381,17 +3381,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Lynda</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Berfelz</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>bencoe01@hotmail.com</t>
+          <t>robandlyndawilson@gmail.com</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3403,17 +3403,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Alpaugh</t>
+          <t>Berfelz</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>tlalpaugh@yahoo.ca</t>
+          <t>bencoe01@hotmail.com</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3425,17 +3425,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Tara</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Snowden</t>
+          <t>Alpaugh</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>sydney.2205.ss@icloud.com</t>
+          <t>tlalpaugh@yahoo.ca</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3447,17 +3447,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Juzar</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ebrahimjee</t>
+          <t>Snowden</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>juzzii@hotmail.com</t>
+          <t>sydney.2205.ss@icloud.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3469,17 +3469,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Juzar</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Ebrahimjee</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>mike_burgess78@hotmail.com</t>
+          <t>juzzii@hotmail.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3491,17 +3491,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>pinglu224@hotmail.com</t>
+          <t>mike_burgess78@hotmail.com</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3513,17 +3513,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Ping</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>smartins2@cogeco.ca</t>
+          <t>pinglu224@hotmail.com</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3535,17 +3535,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Theresa</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Zamora</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>theresazam1@gmail.com</t>
+          <t>smartins2@cogeco.ca</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3557,17 +3557,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Yingmai</t>
+          <t>Theresa</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Guo</t>
+          <t>Zamora</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>guoyingmai@gmail.com</t>
+          <t>theresazam1@gmail.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3579,15 +3579,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Yingmai</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chow</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+          <t>Guo</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>guoyingmai@gmail.com</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3597,19 +3601,15 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>O'Loughlin</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>linda_olo@yahoo.ca</t>
-        </is>
-      </c>
+          <t>Chow</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3619,17 +3619,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Gerry</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tessier</t>
+          <t>O'Loughlin</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>tessiergerry@gmail.com</t>
+          <t>linda_olo@yahoo.ca</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3641,17 +3641,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Gerry</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>De Lucia</t>
+          <t>Tessier</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>steve.delucia@ouitlook.com</t>
+          <t>tessiergerry@gmail.com</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3663,17 +3663,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>nick</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>quartarone</t>
+          <t>De Lucia</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>nickquartarone04@gmail.com</t>
+          <t>steve.delucia@ouitlook.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3685,17 +3685,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Deliah</t>
+          <t>nick</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>McLane</t>
+          <t>quartarone</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>deliah.custodio@icloud.com</t>
+          <t>nickquartarone04@gmail.com</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3707,15 +3707,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Qianying</t>
+          <t>Deliah</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tang</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>McLane</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>deliah.custodio@icloud.com</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3725,19 +3729,15 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sadi</t>
+          <t>Qianying</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Arbid</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>arbid.arbid@hotmail.com</t>
-        </is>
-      </c>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3747,17 +3747,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Sadi</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jin</t>
+          <t>Arbid</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>xin_jin@hotmail.com</t>
+          <t>arbid.arbid@hotmail.com</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3769,17 +3769,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Harsh</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Jin</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>harsh.canada2018@gmail.com</t>
+          <t>xin_jin@hotmail.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3791,17 +3791,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Harsh</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>tiger.liuy@gmail.com</t>
+          <t>harsh.canada2018@gmail.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3813,17 +3813,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Jinhee</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>kinikini0429@gmail.com</t>
+          <t>tiger.liuy@gmail.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3835,17 +3835,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RAIKO</t>
+          <t>Jinhee</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>raikolee@gmail.com</t>
+          <t>kinikini0429@gmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3857,17 +3857,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>RAIKO</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Lico</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>jacobjlico@outlook.com</t>
+          <t>raikolee@gmail.com</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3879,17 +3879,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>nathalie</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>devault-arbid</t>
+          <t>Lico</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>devault.devault@hotmail.com</t>
+          <t>jacobjlico@outlook.com</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3901,17 +3901,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>nathalie</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>devault-arbid</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>alimiller314@gmail.com</t>
+          <t>devault.devault@hotmail.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3923,17 +3923,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Xie</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>cynthia.xie@gmail.com</t>
+          <t>alimiller314@gmail.com</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3945,17 +3945,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Titei</t>
+          <t>Xie</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>temp.100@live.com</t>
+          <t>cynthia.xie@gmail.com</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3967,17 +3967,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>Titei</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>tinarainbox@hotmail.com</t>
+          <t>temp.100@live.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3989,17 +3989,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Marchese</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>marchese.ash@gmail.com</t>
+          <t>tinarainbox@hotmail.com</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4011,17 +4011,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Zamzam</t>
+          <t>Marchese</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>omarrzamzam@gmail.com</t>
+          <t>marchese.ash@gmail.com</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Yena</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Zamzam</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ynhk1127@gmail.com</t>
+          <t>omarrzamzam@gmail.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4055,17 +4055,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Yena</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Montalbano</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>amontalbano75@gmail.com</t>
+          <t>ynhk1127@gmail.com</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4077,17 +4077,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Montalbano</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>luke.d.everest@gmail.com</t>
+          <t>amontalbano75@gmail.com</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4099,17 +4099,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tse</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>nathantse@live.com</t>
+          <t>luke.d.everest@gmail.com</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4121,17 +4121,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Farid</t>
+          <t>Tse</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>aawad62@gmail.com</t>
+          <t>nathantse@live.com</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4143,17 +4143,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Cox</t>
+          <t>Farid</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ethancox1337@gmail.com</t>
+          <t>aawad62@gmail.com</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4165,17 +4165,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Akl</t>
+          <t>Cox</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>mohamedakl99@gmail.com</t>
+          <t>ethancox1337@gmail.com</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4187,17 +4187,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ron</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>borbas</t>
+          <t>Akl</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ronborbas@gmail.com</t>
+          <t>mohamedakl99@gmail.com</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4209,17 +4209,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>katelyn</t>
+          <t>ron</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>chung</t>
+          <t>borbas</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>katelynchung99@gmail.com</t>
+          <t>ronborbas@gmail.com</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4231,17 +4231,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>katelyn</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>chung</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>wangkejuan@hotmail.com</t>
+          <t>katelynchung99@gmail.com</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4253,17 +4253,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Oana</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Titei</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>oana@titei.com</t>
+          <t>wangkejuan@hotmail.com</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4275,17 +4275,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Oana</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Hyravy</t>
+          <t>Titei</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>nikkihyravy@gmail.com</t>
+          <t>oana@titei.com</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4297,17 +4297,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>jason</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Hyravy</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>jasonbear34@live.ca</t>
+          <t>nikkihyravy@gmail.com</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4319,17 +4319,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>jerry</t>
+          <t>jason</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>jerry.hm@hotmail.com</t>
+          <t>jasonbear34@live.ca</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4341,17 +4341,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>jerry</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Guillemette</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>rogerguillemette@yahoo.ca</t>
+          <t>jerry.hm@hotmail.com</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4363,17 +4363,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>bq</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>xu</t>
+          <t>Guillemette</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>mr.bq.xu@gmail.com</t>
+          <t>rogerguillemette@yahoo.ca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4385,17 +4385,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>bq</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>gallucci</t>
+          <t>xu</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>j_delcol@yahoo.ca</t>
+          <t>mr.bq.xu@gmail.com</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4407,17 +4407,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>gallucci</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>mh@intersurgical.ca</t>
+          <t>j_delcol@yahoo.ca</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4429,17 +4429,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Montalbano</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>linda@graffretail.com</t>
+          <t>mh@intersurgical.ca</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4451,17 +4451,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>matheus</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>krumme</t>
+          <t>Montalbano</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>mjkrumme@gmail.com</t>
+          <t>linda@graffretail.com</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4473,17 +4473,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>matheus</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>krumme</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>wangkejuan+@hotmail.com</t>
+          <t>mjkrumme@gmail.com</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4495,17 +4495,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>alexander</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>chung</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>alexanderchung88@gmail.com</t>
+          <t>wangkejuan+@hotmail.com</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4517,17 +4517,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>alexander</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>chung</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>jamekoch9@gmail.com</t>
+          <t>alexanderchung88@gmail.com</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4539,17 +4539,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>shuang</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>yao</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>stevenyaomolins@hotmail.com</t>
+          <t>jamekoch9@gmail.com</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4561,17 +4561,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Sherif</t>
+          <t>shuang</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Shama</t>
+          <t>yao</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>sherifshama@me.com</t>
+          <t>stevenyaomolins@hotmail.com</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4583,17 +4583,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Sherif</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>El</t>
+          <t>Shama</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>amahalwy@gmail.com</t>
+          <t>sherifshama@me.com</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4605,17 +4605,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Compas</t>
+          <t>El</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>joshcompas@outlook.com</t>
+          <t>amahalwy@gmail.com</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4627,17 +4627,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>donna</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>petrarca</t>
+          <t>Compas</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>julesmom@hotmail.com</t>
+          <t>joshcompas@outlook.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4649,17 +4649,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>donna</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Boal</t>
+          <t>petrarca</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>eboal@bell.net</t>
+          <t>julesmom@hotmail.com</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4671,17 +4671,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Gasparik</t>
+          <t>Boal</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>tgasparik@cogeco.ca</t>
+          <t>eboal@bell.net</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4693,17 +4693,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Tara</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hu</t>
+          <t>Gasparik</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>claudia.nrsg@gmail.com</t>
+          <t>tgasparik@cogeco.ca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4715,17 +4715,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Lo</t>
+          <t>Hu</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>justinhllo10@gmail.com</t>
+          <t>claudia.nrsg@gmail.com</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4737,17 +4737,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Vander Velden</t>
+          <t>Lo</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>stewvelden@gmail.com</t>
+          <t>justinhllo10@gmail.com</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4759,20 +4759,328 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Vander Velden</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>stewvelden@gmail.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>mohfouad01@gmail.com</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Ljubisic</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>rob.ljubisic@outlook.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Avni</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Dixit</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>avnidixit@gmail.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Claire</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>peterandclare@gmail.com</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Jowahir</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>peter.jowahir@gmail.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Baldock</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>kbahula@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Jasmine</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Jowahir</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>jasmine.jowahir@gmail.com</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Judi</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Laman</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>judilynnv@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Niya</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Jowahir</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>njowahir88@gmail.com</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Tonogai</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>jtonogai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sebesta</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>legsebesta@gmail.com</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Qian</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>yrqian@gmail.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>aomar6197@gmail.com</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Dorthy</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ddliu75@gmail.com</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Burloak.xlsx
+++ b/docs/downloads/Burloak.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Ebidia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jan.canada2005@gmail.com</t>
+          <t>jamesebidia@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sandi</t>
+          <t>KImberly</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Savage Paulson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sandi@pickleplexclub.ca</t>
+          <t>kim@paulsons.ca</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shayaan</t>
+          <t>Sora</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alibhai</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>shayaan.alibhai@gmail.com</t>
+          <t>sorasmith71@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Goldsack</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lggoldsack@gmail.com</t>
+          <t>jan.canada2005@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MCTEAR</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sales@prothane.ca</t>
+          <t>sandi@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Shayaan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gooding</t>
+          <t>Alibhai</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>thecoachgooding@gmail.com</t>
+          <t>shayaan.alibhai@gmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Imtiaz</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alibhai</t>
+          <t>Hanczyk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>imtiaz.alibhai@gmail.com</t>
+          <t>hanczykkennedy@yahoo.ca</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tashya</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sison</t>
+          <t>Gottfried</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tashyacaleon@gmail.com</t>
+          <t>markgottfried63@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sHENDOSH</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MADHUSUDHAN</t>
+          <t>Goldsack</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>shendoshm@gmail.com</t>
+          <t>lggoldsack@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>MCTEAR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dannyjose@me.com</t>
+          <t>sales@prothane.ca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Gooding</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>chant.j09@gmail.com</t>
+          <t>thecoachgooding@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,15 +743,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Kawamoto</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ljkawamoto@gmail.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -761,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Imtiaz</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>Alibhai</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nixon_greg@yahoo.ca</t>
+          <t>imtiaz.alibhai@gmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -783,15 +787,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cole</t>
+          <t>Roanna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chong</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>delos santos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>roanna_wacks@yahoo.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -801,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Tashya</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Choy</t>
+          <t>Sison</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jacob.choy@live.ca</t>
+          <t>tashyacaleon@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -823,15 +831,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>brendan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Irianto</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>cummins</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bcummins@rogers.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -841,15 +853,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Croswell</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jennyrcroswell@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -859,15 +875,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Liliana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Irianto</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Tatulea</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ltatulea@gmail.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -877,15 +897,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dez</t>
+          <t>sHENDOSH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lopez</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>MADHUSUDHAN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>shendoshm@gmail.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -895,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lopez</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jasonlopez53@hotmail.com</t>
+          <t>dannyjose@me.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -917,15 +941,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Yiyun</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Morris</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jeff.morris.yyz@gmail.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -935,15 +963,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Chant</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>chant.j09@gmail.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -953,15 +985,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aashir</t>
+          <t>Vasu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Meeran</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Sutharsan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>svasugan@gmail.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -971,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Cheryl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Ebidia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>liuyingalice@gmail.com</t>
+          <t>cheryl0077@hotmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -993,19 +1029,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Scott David</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Worden</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>sworden@multimatic.com</t>
-        </is>
-      </c>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1015,15 +1047,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Manny</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Virtudazo</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Nixon</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nixon_greg@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1033,19 +1069,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>cole</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Burford</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>markch58@gmail.com</t>
-        </is>
-      </c>
+          <t>Chong</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1055,17 +1087,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lynne</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Maksuta</t>
+          <t>Choy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lsharp2@cogeco.ca</t>
+          <t>jacob.choy@live.ca</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1077,19 +1109,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Joyce</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>amandamariejoyce@gmail.com</t>
-        </is>
-      </c>
+          <t>Irianto</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1099,19 +1127,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dat</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pham</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>datpham.ca@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1121,19 +1145,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cherio</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>My</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>cherio.my@gmail.com</t>
-        </is>
-      </c>
+          <t>Irianto</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1143,19 +1163,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ilona</t>
+          <t>Dez</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Judeikiene</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ilona0311@gmail.com</t>
-        </is>
-      </c>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1165,15 +1181,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cam</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jasonlopez53@hotmail.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1183,12 +1203,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Yiyun</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1201,19 +1221,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rafat</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Abu-Zeineh</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>rafat.abuzeineh@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1223,19 +1239,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Aashir</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vit</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>annevit.av@icloud.com</t>
-        </is>
-      </c>
+          <t>Meeran</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1245,15 +1257,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Uyen</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Diep</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>liuyingalice@gmail.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1263,17 +1279,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Scott David</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Worden</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ryanhan821@yahoo.com</t>
+          <t>sworden@multimatic.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1285,19 +1301,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Manny</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quinsay</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>r.quinsay@gmail.com</t>
-        </is>
-      </c>
+          <t>Virtudazo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1307,17 +1319,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Yong</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Burford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jiangyong1998@hotmail.com</t>
+          <t>markch58@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1329,15 +1341,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maliyah</t>
+          <t>Lynne</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jeshani</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Maksuta</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lsharp2@cogeco.ca</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1347,17 +1363,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Xin</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deng</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>cindydeng322@gmail.com</t>
+          <t>amandamariejoyce@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1369,17 +1385,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jeanette</t>
+          <t>Dat</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Perez</t>
+          <t>Pham</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jeanetteperez72@gmail.com</t>
+          <t>datpham.ca@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1391,15 +1407,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Cherio</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saad</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>My</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cherio.my@gmail.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1409,17 +1429,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bibi</t>
+          <t>Ilona</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Popovic</t>
+          <t>Judeikiene</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>biba018@rogers.com</t>
+          <t>ilona0311@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1431,19 +1451,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Haidan</t>
+          <t>cam</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>haiden_wang@hotmail.ca</t>
-        </is>
-      </c>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1453,12 +1469,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hu</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1471,15 +1487,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Rafat</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rutter</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Abu-Zeineh</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>rafat.abuzeineh@gmail.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1489,17 +1509,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>deanna</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>badovinac</t>
+          <t>Vit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dbadovinac@fibercast.com</t>
+          <t>annevit.av@icloud.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1511,19 +1531,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Uyen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vucic</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>kathy@parass.com</t>
-        </is>
-      </c>
+          <t>Diep</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1533,17 +1549,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>brucehankmoore@gmail.com</t>
+          <t>ryanhan821@yahoo.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1555,17 +1571,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gilligan</t>
+          <t>Quinsay</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kevin6862@hotmail.com</t>
+          <t>r.quinsay@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1577,17 +1593,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Yong</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mary.kelly.remax@gmail.com</t>
+          <t>jiangyong1998@hotmail.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1599,12 +1615,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Maliyah</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Jeshani</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1617,17 +1633,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Xin</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kvesic</t>
+          <t>Deng</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>knezic_zeljka@yahoo.com</t>
+          <t>cindydeng322@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1639,17 +1655,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>steve</t>
+          <t>Jeanette</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kelly</t>
+          <t>Perez</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>steve.wayne.kelly@gmail.com</t>
+          <t>jeanetteperez72@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1661,12 +1677,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Baraa</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1679,15 +1695,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Bibi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Samuels</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>Popovic</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>biba018@rogers.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1697,15 +1717,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Nataly</t>
+          <t>Haidan</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>haiden_wang@hotmail.ca</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1715,12 +1739,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Hu</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1733,19 +1757,15 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bantin</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>colincbantin@gmail.com</t>
-        </is>
-      </c>
+          <t>Rutter</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1755,15 +1775,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>deanna</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Froats</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>badovinac</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>dbadovinac@fibercast.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1773,17 +1797,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Vucic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>larrymhenderson@gmail.com</t>
+          <t>kathy@parass.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1795,17 +1819,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Modi</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bonnie.modi@gmail.com</t>
+          <t>brucehankmoore@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1817,15 +1841,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ross</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Gilligan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>kevin6862@hotmail.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1835,15 +1863,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Elliot</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Whittington</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>mary.kelly.remax@gmail.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1853,12 +1885,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1871,15 +1903,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Kvesic</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>knezic_zeljka@yahoo.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1889,15 +1925,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>steve</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Velanoff</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>steve.wayne.kelly@gmail.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1907,12 +1947,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Edlyn</t>
+          <t>Baraa</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1925,19 +1965,15 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kijak</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>petey.kijak@gmail.com</t>
-        </is>
-      </c>
+          <t>Samuels</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1947,12 +1983,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Nataly</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sapra</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1965,19 +2001,15 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ella Rose</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>rmakrma@gmail.com</t>
-        </is>
-      </c>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1987,15 +2019,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jacqueline</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Bantin</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>colincbantin@gmail.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2005,12 +2041,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Froats</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2023,15 +2059,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Prendergast</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>larrymhenderson@gmail.com</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2041,15 +2081,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Prendergast</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Modi</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>bonnie.modi@gmail.com</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2059,12 +2103,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Oren</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lasko</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2077,12 +2121,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Oshra</t>
+          <t>Elliot</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lasko</t>
+          <t>Whittington</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2095,19 +2139,15 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Flowers</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>jjflowers@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Von Zuben</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2117,19 +2157,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>antony</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>han</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>uw.antony@gmail.com</t>
-        </is>
-      </c>
+          <t>Von Zuben</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2139,12 +2175,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Velanoff</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2157,12 +2193,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Haichen (Henry)</t>
+          <t>Edlyn</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2175,17 +2211,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Divya</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kwatra</t>
+          <t>Kijak</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>diiu@hotmail.com</t>
+          <t>petey.kijak@gmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2197,19 +2233,15 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McMillan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>jackmcmi17@gmail.com</t>
-        </is>
-      </c>
+          <t>Sapra</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2219,17 +2251,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Ella Rose</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Costa</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>fabian.pagani@icloud.com</t>
+          <t>rmakrma@gmail.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2241,19 +2273,15 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Melody</t>
+          <t>Jacqueline</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>melody2250hotmail@hotmail.com</t>
-        </is>
-      </c>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2263,19 +2291,15 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>justin</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>bradt</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>justinbradt@gmail.com</t>
-        </is>
-      </c>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2285,12 +2309,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Quach</t>
+          <t>Prendergast</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2303,12 +2327,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Griffith</t>
+          <t>Prendergast</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2321,17 +2345,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>ponikvar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>scrappiedoo10@hotmail.com</t>
+          <t>ponikvarsa@gmail.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2343,12 +2367,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Oren</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Lasko</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2361,12 +2385,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Oshra</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deir</t>
+          <t>Lasko</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2379,17 +2403,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dhir</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kothari</t>
+          <t>Flowers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>mr.dhirkothari@gmail.com</t>
+          <t>jjflowers@hotmail.ca</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2401,17 +2425,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>antony</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>morgan</t>
+          <t>han</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>brian.k.morgan@hotmail.com</t>
+          <t>uw.antony@gmail.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2423,19 +2447,15 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>cvbaker@hotmail.com</t>
-        </is>
-      </c>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2445,19 +2465,15 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Haichen (Henry)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bobbitt</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>amy.bobbitt@ig.ca</t>
-        </is>
-      </c>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2467,15 +2483,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Arvind</t>
+          <t>Divya</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kochar</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>Kwatra</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>diiu@hotmail.com</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2485,17 +2505,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>pinto</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>leogbarone@icloud.com</t>
+          <t>jackmcmi17@gmail.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2507,15 +2527,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Royan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>fabian.pagani@icloud.com</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2525,15 +2549,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Arhaan</t>
+          <t>Melody</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jinnah</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>melody2250hotmail@hotmail.com</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2543,15 +2571,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Arham</t>
+          <t>justin</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jinnah</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>bradt</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>justinbradt@gmail.com</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2561,12 +2593,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hillmer</t>
+          <t>Quach</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2579,12 +2611,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Gail</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deary-Yu</t>
+          <t>Griffith</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2597,15 +2629,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Perevalova</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>scrappiedoo10@hotmail.com</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2615,12 +2651,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hillmer</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2633,19 +2669,15 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Pitt</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>barbpitt21@gmail.com</t>
-        </is>
-      </c>
+          <t>Deir</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2655,17 +2687,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Dhir</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Defrang</t>
+          <t>Kothari</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>rolanddefrang@icloud.com</t>
+          <t>mr.dhirkothari@gmail.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2677,17 +2709,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Eunice</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Dayrit</t>
+          <t>morgan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>eunicereniel_d@yahoo.com</t>
+          <t>brian.k.morgan@hotmail.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2699,15 +2731,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Eason</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Han</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>cvbaker@hotmail.com</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2717,17 +2753,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Bobbitt</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>katwalker04@gmail.com</t>
+          <t>amy.bobbitt@ig.ca</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2739,19 +2775,15 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Arvind</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Walker</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>walker.cm.jake@gmail.com</t>
-        </is>
-      </c>
+          <t>Kochar</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2761,15 +2793,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hamilton</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>pinto</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>leogbarone@icloud.com</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2779,12 +2815,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Heidi</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Plouffe</t>
+          <t>Royan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2797,12 +2833,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Aimee</t>
+          <t>Arhaan</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Porter</t>
+          <t>Jinnah</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2815,19 +2851,15 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Keyana</t>
+          <t>Arham</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Segato</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>kfsegato@icloud.com</t>
-        </is>
-      </c>
+          <t>Jinnah</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2837,19 +2869,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Seana</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Maennling</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>seanamaennling@icloud.com</t>
-        </is>
-      </c>
+          <t>Hillmer</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2859,19 +2887,15 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>gregc@pickleplex.ca</t>
-        </is>
-      </c>
+          <t>Deary-Yu</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2881,19 +2905,15 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Mikaal</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ansari</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>ansari.mikaal@gmail.com</t>
-        </is>
-      </c>
+          <t>Perevalova</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2903,19 +2923,15 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Aayan</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>bonilla</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>1bonillacaay@hdsb.ca</t>
-        </is>
-      </c>
+          <t>Hillmer</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2925,15 +2941,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>Pitt</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>barbpitt21@gmail.com</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2943,17 +2963,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Donnelly</t>
+          <t>Defrang</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jdonnellybcba@gmail.com</t>
+          <t>rolanddefrang@icloud.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2965,17 +2985,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AUBREE</t>
+          <t>Eunice</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FRANCIS</t>
+          <t>Dayrit</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>aubsfrancis10@gmail.com</t>
+          <t>eunicereniel_d@yahoo.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -2987,12 +3007,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Brydon</t>
+          <t>Eason</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3005,15 +3025,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Fang</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>katwalker04@gmail.com</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3023,15 +3047,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Eddie</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>walker.cm.jake@gmail.com</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3041,12 +3069,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Daren</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3059,12 +3087,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Aubree</t>
+          <t>Heidi</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Plouffe</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3077,19 +3105,15 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Stefano</t>
+          <t>Aimee</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bomben</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>stefbomben@gmail.com</t>
-        </is>
-      </c>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3099,17 +3123,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>matthew</t>
+          <t>Keyana</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nesbitt</t>
+          <t>Segato</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>mnesbitt@cogeco.ca</t>
+          <t>kfsegato@icloud.com</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3121,17 +3145,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tania</t>
+          <t>Seana</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>tani</t>
+          <t>Maennling</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ttani066@gmail.com</t>
+          <t>seanamaennling@icloud.com</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3143,17 +3167,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Parm</t>
+          <t>Mikaal</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Ansari</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>parm76@hotmail.com</t>
+          <t>ansari.mikaal@gmail.com</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3165,17 +3189,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Aayan</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Bartlett</t>
+          <t>bonilla</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jdbartlett@gmail.com</t>
+          <t>1bonillacaay@hdsb.ca</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3187,19 +3211,15 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NOURA</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BALBAA</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>balbaanoura@gmail.com</t>
-        </is>
-      </c>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3209,15 +3229,19 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Rene</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Quercia</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>Donnelly</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jdonnellybcba@gmail.com</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3227,17 +3251,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>AUBREE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>McGuire</t>
+          <t>FRANCIS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>mcguire11170@gmail.com</t>
+          <t>aubsfrancis10@gmail.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3249,19 +3273,15 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>jessica</t>
+          <t>Brydon</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>rickus</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>jess.rickus@gmail.com</t>
-        </is>
-      </c>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3271,19 +3291,15 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Fang</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>riccimatthew95@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3293,19 +3309,15 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Eddie</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Moazzam</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>zara.moazzam.16@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3315,19 +3327,15 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lindsay</t>
+          <t>Daren</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Hooper</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>lindsayhooper79@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3337,19 +3345,15 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CHANDRE</t>
+          <t>Aubree</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MACDOUGALL</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>chandre@gmail.com</t>
-        </is>
-      </c>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3359,17 +3363,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Stefano</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Magagna</t>
+          <t>Bomben</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>marina45@rogers.com</t>
+          <t>stefbomben@gmail.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3381,17 +3385,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Lynda</t>
+          <t>matthew</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>nesbitt</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>robandlyndawilson@gmail.com</t>
+          <t>mnesbitt@cogeco.ca</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3403,17 +3407,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>tania</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Berfelz</t>
+          <t>tani</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>bencoe01@hotmail.com</t>
+          <t>ttani066@gmail.com</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3425,17 +3429,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>Gloria</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Alpaugh</t>
+          <t>Tomlinson</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>tlalpaugh@yahoo.ca</t>
+          <t>gloria.tomlinson@gmail.com</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3447,17 +3451,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Parm</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Snowden</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>sydney.2205.ss@icloud.com</t>
+          <t>parm76@hotmail.com</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3469,17 +3473,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Juzar</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ebrahimjee</t>
+          <t>Bartlett</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>juzzii@hotmail.com</t>
+          <t>jdbartlett@gmail.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3491,17 +3495,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>NOURA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>BALBAA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>mike_burgess78@hotmail.com</t>
+          <t>balbaanoura@gmail.com</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3513,19 +3517,15 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>Rene</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lu</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>pinglu224@hotmail.com</t>
-        </is>
-      </c>
+          <t>Quercia</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3535,17 +3535,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>McGuire</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>smartins2@cogeco.ca</t>
+          <t>mcguire11170@gmail.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3557,17 +3557,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Theresa</t>
+          <t>jessica</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Zamora</t>
+          <t>rickus</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>theresazam1@gmail.com</t>
+          <t>jess.rickus@gmail.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3579,17 +3579,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Yingmai</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Guo</t>
+          <t>Armena</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>guoyingmai@gmail.com</t>
+          <t>chrisarmena@gmail.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3601,15 +3601,19 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Chow</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>riccimatthew95@gmail.com</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3619,17 +3623,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>O'Loughlin</t>
+          <t>Moazzam</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>linda_olo@yahoo.ca</t>
+          <t>zara.moazzam.16@gmail.com</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3641,17 +3645,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Gerry</t>
+          <t>Lindsay</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tessier</t>
+          <t>Hooper</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>tessiergerry@gmail.com</t>
+          <t>lindsayhooper79@gmail.com</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3663,17 +3667,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>CHANDRE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>De Lucia</t>
+          <t>MACDOUGALL</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>steve.delucia@ouitlook.com</t>
+          <t>chandre@gmail.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3685,17 +3689,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>nick</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>quartarone</t>
+          <t>Magagna</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>nickquartarone04@gmail.com</t>
+          <t>marina45@rogers.com</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3707,17 +3711,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Deliah</t>
+          <t>Lynda</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>McLane</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>deliah.custodio@icloud.com</t>
+          <t>robandlyndawilson@gmail.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3729,15 +3733,19 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Qianying</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tang</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
+          <t>Berfelz</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>bencoe01@hotmail.com</t>
+        </is>
+      </c>
       <c r="D162" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3747,17 +3755,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sadi</t>
+          <t>Tara</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Arbid</t>
+          <t>Alpaugh</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>arbid.arbid@hotmail.com</t>
+          <t>tlalpaugh@yahoo.ca</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3769,17 +3777,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Jin</t>
+          <t>Snowden</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>xin_jin@hotmail.com</t>
+          <t>sydney.2205.ss@icloud.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3791,17 +3799,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Harsh</t>
+          <t>Juzar</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Ebrahimjee</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>harsh.canada2018@gmail.com</t>
+          <t>juzzii@hotmail.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3813,17 +3821,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>tiger.liuy@gmail.com</t>
+          <t>mike_burgess78@hotmail.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3835,17 +3843,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Jinhee</t>
+          <t>Ping</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>kinikini0429@gmail.com</t>
+          <t>pinglu224@hotmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3857,17 +3865,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RAIKO</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>raikolee@gmail.com</t>
+          <t>smartins2@cogeco.ca</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3879,17 +3887,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Theresa</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Lico</t>
+          <t>Zamora</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>jacobjlico@outlook.com</t>
+          <t>theresazam1@gmail.com</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3901,17 +3909,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>nathalie</t>
+          <t>Yingmai</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>devault-arbid</t>
+          <t>Guo</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>devault.devault@hotmail.com</t>
+          <t>guoyingmai@gmail.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3923,19 +3931,15 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Miller</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>alimiller314@gmail.com</t>
-        </is>
-      </c>
+          <t>Chow</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3945,17 +3949,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Xie</t>
+          <t>O'Loughlin</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>cynthia.xie@gmail.com</t>
+          <t>linda_olo@yahoo.ca</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3967,17 +3971,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Gerry</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Titei</t>
+          <t>Tessier</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>temp.100@live.com</t>
+          <t>tessiergerry@gmail.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3989,17 +3993,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>De Lucia</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>tinarainbox@hotmail.com</t>
+          <t>steve.delucia@ouitlook.com</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4011,17 +4015,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>nick</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Marchese</t>
+          <t>quartarone</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>marchese.ash@gmail.com</t>
+          <t>nickquartarone04@gmail.com</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4033,17 +4037,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Deliah</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Zamzam</t>
+          <t>McLane</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>omarrzamzam@gmail.com</t>
+          <t>deliah.custodio@icloud.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4055,19 +4059,15 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Yena</t>
+          <t>Qianying</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>ynhk1127@gmail.com</t>
-        </is>
-      </c>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -4077,17 +4077,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Sadi</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Montalbano</t>
+          <t>Arbid</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>amontalbano75@gmail.com</t>
+          <t>arbid.arbid@hotmail.com</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4099,17 +4099,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Jin</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>luke.d.everest@gmail.com</t>
+          <t>xin_jin@hotmail.com</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4121,17 +4121,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Harsh</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Tse</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>nathantse@live.com</t>
+          <t>harsh.canada2018@gmail.com</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4143,17 +4143,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Farid</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>aawad62@gmail.com</t>
+          <t>tiger.liuy@gmail.com</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4165,17 +4165,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Jinhee</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Cox</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ethancox1337@gmail.com</t>
+          <t>kinikini0429@gmail.com</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4187,17 +4187,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>RAIKO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Akl</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>mohamedakl99@gmail.com</t>
+          <t>raikolee@gmail.com</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4209,17 +4209,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ron</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>borbas</t>
+          <t>Lico</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ronborbas@gmail.com</t>
+          <t>jacobjlico@outlook.com</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4231,17 +4231,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>katelyn</t>
+          <t>nathalie</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>chung</t>
+          <t>devault-arbid</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>katelynchung99@gmail.com</t>
+          <t>devault.devault@hotmail.com</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4253,17 +4253,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>wangkejuan@hotmail.com</t>
+          <t>alimiller314@gmail.com</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4275,17 +4275,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Oana</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Titei</t>
+          <t>Xie</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>oana@titei.com</t>
+          <t>cynthia.xie@gmail.com</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4297,17 +4297,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Hyravy</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>nikkihyravy@gmail.com</t>
+          <t>jeff74hedley@gmail.com</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4319,17 +4319,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>jason</t>
+          <t>Crosby</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>jasonbear34@live.ca</t>
+          <t>crosby.gibson@rogers.com</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4341,17 +4341,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>jerry</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>Titei</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>jerry.hm@hotmail.com</t>
+          <t>temp.100@live.com</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4363,17 +4363,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Guillemette</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>rogerguillemette@yahoo.ca</t>
+          <t>tinarainbox@hotmail.com</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4385,17 +4385,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>bq</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>xu</t>
+          <t>Marchese</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>mr.bq.xu@gmail.com</t>
+          <t>marchese.ash@gmail.com</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4407,17 +4407,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>gallucci</t>
+          <t>Zamzam</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>j_delcol@yahoo.ca</t>
+          <t>omarrzamzam@gmail.com</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4429,17 +4429,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Yena</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>mh@intersurgical.ca</t>
+          <t>ynhk1127@gmail.com</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4451,7 +4451,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>linda@graffretail.com</t>
+          <t>amontalbano75@gmail.com</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4473,17 +4473,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>matheus</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>krumme</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>mjkrumme@gmail.com</t>
+          <t>luke.d.everest@gmail.com</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4495,17 +4495,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>Tse</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>wangkejuan+@hotmail.com</t>
+          <t>nathantse@live.com</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4517,17 +4517,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>alexander</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>chung</t>
+          <t>Farid</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>alexanderchung88@gmail.com</t>
+          <t>aawad62@gmail.com</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4539,17 +4539,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Cox</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>jamekoch9@gmail.com</t>
+          <t>ethancox1337@gmail.com</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4561,17 +4561,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>shuang</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>yao</t>
+          <t>Akl</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>stevenyaomolins@hotmail.com</t>
+          <t>mohamedakl99@gmail.com</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4583,17 +4583,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Sherif</t>
+          <t>ron</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Shama</t>
+          <t>borbas</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>sherifshama@me.com</t>
+          <t>ronborbas@gmail.com</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4605,17 +4605,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>katelyn</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>El</t>
+          <t>chung</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>amahalwy@gmail.com</t>
+          <t>katelynchung99@gmail.com</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4627,17 +4627,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Compas</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>joshcompas@outlook.com</t>
+          <t>wangkejuan@hotmail.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4649,17 +4649,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>donna</t>
+          <t>Oana</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>petrarca</t>
+          <t>Titei</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>julesmom@hotmail.com</t>
+          <t>oana@titei.com</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4671,17 +4671,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Boal</t>
+          <t>Hyravy</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>eboal@bell.net</t>
+          <t>nikkihyravy@gmail.com</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4693,17 +4693,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>jason</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Gasparik</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>tgasparik@cogeco.ca</t>
+          <t>jasonbear34@live.ca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4715,17 +4715,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>jerry</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hu</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>claudia.nrsg@gmail.com</t>
+          <t>jerry.hm@hotmail.com</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4737,17 +4737,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Lo</t>
+          <t>Guillemette</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>justinhllo10@gmail.com</t>
+          <t>rogerguillemette@yahoo.ca</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4759,17 +4759,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>bq</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Vander Velden</t>
+          <t>xu</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>stewvelden@gmail.com</t>
+          <t>mr.bq.xu@gmail.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4781,17 +4781,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Sa</t>
+          <t>gallucci</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>mohfouad01@gmail.com</t>
+          <t>j_delcol@yahoo.ca</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4803,17 +4803,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Ljubisic</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>rob.ljubisic@outlook.com</t>
+          <t>mh@intersurgical.ca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -4825,17 +4825,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Avni</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Dixit</t>
+          <t>Montalbano</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>avnidixit@gmail.com</t>
+          <t>linda@graffretail.com</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -4847,17 +4847,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>matheus</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>krumme</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>peterandclare@gmail.com</t>
+          <t>mjkrumme@gmail.com</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -4869,17 +4869,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Jowahir</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>peter.jowahir@gmail.com</t>
+          <t>wangkejuan+@hotmail.com</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -4891,17 +4891,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>alexander</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Baldock</t>
+          <t>chung</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>kbahula@hotmail.com</t>
+          <t>alexanderchung88@gmail.com</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Jowahir</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>jasmine.jowahir@gmail.com</t>
+          <t>jamekoch9@gmail.com</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4935,17 +4935,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Judi</t>
+          <t>shuang</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Laman</t>
+          <t>yao</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>judilynnv@hotmail.com</t>
+          <t>stevenyaomolins@hotmail.com</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -4957,17 +4957,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Niya</t>
+          <t>Sherif</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Jowahir</t>
+          <t>Shama</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>njowahir88@gmail.com</t>
+          <t>sherifshama@me.com</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -4979,17 +4979,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Tonogai</t>
+          <t>El</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>jtonogai@gmail.com</t>
+          <t>amahalwy@gmail.com</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5001,17 +5001,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Sebesta</t>
+          <t>Compas</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>legsebesta@gmail.com</t>
+          <t>joshcompas@outlook.com</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5023,17 +5023,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>donna</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Qian</t>
+          <t>petrarca</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>yrqian@gmail.com</t>
+          <t>julesmom@hotmail.com</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5045,17 +5045,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Boal</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>aomar6197@gmail.com</t>
+          <t>eboal@bell.net</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5067,20 +5067,1904 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Gasparik</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>tgasparik@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Claudia</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Hu</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>claudia.nrsg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Lo</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>justinhllo10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Vander Velden</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>stewvelden@gmail.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Sa</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>mohfouad01@gmail.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Ljubisic</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>rob.ljubisic@outlook.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Avni</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Dixit</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>avnidixit@gmail.com</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Claire</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>peterandclare@gmail.com</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Jowahir</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>peter.jowahir@gmail.com</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Baldock</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>kbahula@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Jasmine</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Jowahir</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>jasmine.jowahir@gmail.com</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Judi</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Laman</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>judilynnv@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Niya</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Jowahir</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>njowahir88@gmail.com</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Tonogai</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>jtonogai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sebesta</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>legsebesta@gmail.com</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Qian</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>yrqian@gmail.com</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>aomar6197@gmail.com</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
           <t>Dorthy</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>Liu</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>ddliu75@gmail.com</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ryanrev86@gmail.com</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>maliya</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>holder</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>maliyaholder1587@gmail.com</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Sprah</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ktsprah@gmail.com</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Sprah</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>tksprah@gmail.com</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>adam</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>quarrington</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>adamq1729@gmail.com</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Nerissa</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Bogdanis</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>nerissab1223@gmail.com</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Teo</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Spady</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>mspaady13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>LeeAnn</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Oleary</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>leeannoleary3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Bullock</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>dwbulock1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>krev@live.ca</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Mya</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Rinaldo</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>mlr03@icloud.com</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>GIRISH</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>PURI</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>girishpuri15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Brankovic</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>rebecca.brankovic8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Norene</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>jnmassey@bell.net</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Lydia</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>lydialiu0110@gmail.com</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Mackenzie</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Solomon</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>mackenziesolomonn@gmail.com</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Hoover</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>ashyhoovy@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Nathan</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Solomon</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>nsolom4@uwo.ca</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Madi</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Fulop</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>madisonfulop@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>john.massey61@gmail.com</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Renee</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Ren</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Louis</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Marck</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>louis@fermarltd.com</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>sean</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>oleary</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>razorhosts@gmail.com</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Draper</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>goaliematty@gmail.com</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Lusk</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>owenlusk61@gmail.com</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>aclayton711@gmail.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>anne</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>leger-smith</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>anne.leger.smith@gmail.com</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Rosanne</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Garrido</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>rosannesells@gmail.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Lacroix</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>lacroix0155@gmail.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Duffield</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>sduffield222@gmail.com</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Russell</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Nawrot</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>russellnawrot@gmail.com</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Andrews</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>kandrews141@gmail.com</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Raymund</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Serina</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>raymundserina@gmail.com</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>cruz</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>davidbcruz@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Kym</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Singlehurst</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>ksinglehurst@me.com</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Dela Vina</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>nancydelavina@gmail.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Jonah</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Sy</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>jsy@cocego.ca</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Dalusong</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>mariedalusong@gmail.com</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Ricky Dela Vina</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>n_dela_vina@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Xin</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>xiangyanli@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Arvin</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Dalusong</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>arvincdal88@gmail.com</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Romeo</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>cruzanova@gmail.com</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Rodel</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>rodmart65@gmail.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Leigh</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Valiente</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>leighvaliente@gmail.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Sharon</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Cancino</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>fstcancino@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jerome</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Magtibay</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>jcmagtibay@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Nassar</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>nassarllc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Armena</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>sheila.armena@icloud.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Bey</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ramzi.beyh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Vien</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Bantog</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>vsbantog@gmail.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Ricky</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Dela Vina</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>megabites0113@gmail.com</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>julia226688@gmail.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Xie</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>frankmxie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>samantha</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>wu</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>samantha.wu@tdsb.on.ca</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Raj</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Pakan</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>rajesh.pakan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Defacendis</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>defacendis@gmail.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>1397099@gmail.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Christina</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Xie</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>tina.christina.xie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Noreen</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Oldfield</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>noreen.oldfield@hotmail.ca</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Xie</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>anthonytxie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Turvey</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Colin</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>cwang1780@gmail.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>susan</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Zhao</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>zyy791115@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>john</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Fu</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>jjjfff0418@gmail.com</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>nicholas.m.ng@gmail.com</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Turvey</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>andturvey@gmail.com</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Huzaifa</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>isahuzaifam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Wu</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>aaronwu751@gmail.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Hellen</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Dong</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>hellen20230810@gmail.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Burloak.xlsx
+++ b/docs/downloads/Burloak.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D309"/>
+  <dimension ref="A1:D387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -457,12 +457,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Johnathan</t>
+          <t>JOHNATHAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SILIVERDIS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ebidia</t>
+          <t>Santella</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jamesebidia@gmail.com</t>
+          <t>nick.santella@gmail.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KImberly</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Savage Paulson</t>
+          <t>Ebidia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kim@paulsons.ca</t>
+          <t>jamesebidia@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sora</t>
+          <t>KImberly</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Savage Paulson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sorasmith71@gmail.com</t>
+          <t>kim@paulsons.ca</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Sora</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jan.canada2005@gmail.com</t>
+          <t>sorasmith71@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandi</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sandi@pickleplexclub.ca</t>
+          <t>jan.canada2005@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shayaan</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alibhai</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shayaan.alibhai@gmail.com</t>
+          <t>sandi@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Imtiaz</t>
+          <t>Roanna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alibhai</t>
+          <t>delos santos</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>imtiaz.alibhai@gmail.com</t>
+          <t>roanna_wacks@yahoo.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Roanna</t>
+          <t>Tashya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>delos santos</t>
+          <t>Sison</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>roanna_wacks@yahoo.com</t>
+          <t>tashyacaleon@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tashya</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sison</t>
+          <t>Gautier</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tashyacaleon@gmail.com</t>
+          <t>saragautier9@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>brendan</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cummins</t>
+          <t>Marasco</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bcummins@rogers.com</t>
+          <t>ldmarasco@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Brendan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Croswell</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jennyrcroswell@yahoo.ca</t>
+          <t>bcummins@rogers.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liliana</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tatulea</t>
+          <t>Croswell</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ltatulea@gmail.com</t>
+          <t>jennyrcroswell@yahoo.ca</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sHENDOSH</t>
+          <t>Liliana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MADHUSUDHAN</t>
+          <t>Tatulea</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>shendoshm@gmail.com</t>
+          <t>ltatulea@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>sHENDOSH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>MADHUSUDHAN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dannyjose@me.com</t>
+          <t>shendoshm@gmail.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Morris</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jeff.morris.yyz@gmail.com</t>
+          <t>dannyjose@me.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chant</t>
+          <t>Morris</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>chant.j09@gmail.com</t>
+          <t>jeff.morris.yyz@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vasu</t>
+          <t>NhatNam</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sutharsan</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>svasugan@gmail.com</t>
+          <t>namnguyen200851@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cheryl</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ebidia</t>
+          <t>Chant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cheryl0077@hotmail.com</t>
+          <t>chant.j09@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,15 +1029,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Vasu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chen</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Sutharsan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>svasugan@gmail.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1047,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Cheryl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nixon</t>
+          <t>Ebidia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nixon_greg@yahoo.ca</t>
+          <t>cheryl0077@hotmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1069,12 +1073,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cole</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chong</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1087,17 +1091,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Choy</t>
+          <t>Nixon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jacob.choy@live.ca</t>
+          <t>nixon_greg@yahoo.ca</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1109,12 +1113,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>cole</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Irianto</t>
+          <t>Chong</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1127,15 +1131,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Choy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jacob.choy@live.ca</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1145,7 +1153,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1163,12 +1171,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dez</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lopez</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1181,19 +1189,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lopez</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>jasonlopez53@hotmail.com</t>
-        </is>
-      </c>
+          <t>Irianto</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1203,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yiyun</t>
+          <t>Dez</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Lopez</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1221,15 +1225,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jasonlopez53@hotmail.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1239,12 +1247,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aashir</t>
+          <t>Yiyun</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Meeran</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1257,19 +1265,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Liu</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>liuyingalice@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1279,19 +1283,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Scott David</t>
+          <t>Aashir</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Worden</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>sworden@multimatic.com</t>
-        </is>
-      </c>
+          <t>Meeran</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1301,15 +1301,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Manny</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Virtudazo</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>liuyingalice@gmail.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1319,17 +1323,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Scott David</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Burford</t>
+          <t>Worden</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>markch58@gmail.com</t>
+          <t>sworden@multimatic.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1341,19 +1345,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lynne</t>
+          <t>Manny</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Maksuta</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>lsharp2@cogeco.ca</t>
-        </is>
-      </c>
+          <t>Virtudazo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1363,17 +1363,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Burford</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>amandamariejoyce@gmail.com</t>
+          <t>markch58@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1385,17 +1385,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dat</t>
+          <t>Lynne</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pham</t>
+          <t>Maksuta</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>datpham.ca@gmail.com</t>
+          <t>lsharp2@cogeco.ca</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1407,17 +1407,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cherio</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>My</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>cherio.my@gmail.com</t>
+          <t>amandamariejoyce@gmail.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1429,17 +1429,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ilona</t>
+          <t>Dat</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Judeikiene</t>
+          <t>Pham</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ilona0311@gmail.com</t>
+          <t>datpham.ca@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1451,15 +1451,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cam</t>
+          <t>Cherio</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>lu</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>My</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>cherio.my@gmail.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1469,15 +1473,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Ilona</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marchetti</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Judeikiene</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ilona0311@gmail.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1487,19 +1495,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rafat</t>
+          <t>cam</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Abu-Zeineh</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>rafat.abuzeineh@gmail.com</t>
-        </is>
-      </c>
+          <t>lu</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1509,19 +1513,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vit</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>annevit.av@icloud.com</t>
-        </is>
-      </c>
+          <t>Marchetti</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1531,15 +1531,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Uyen</t>
+          <t>Rafat</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Diep</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Abu-Zeineh</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>rafat.abuzeineh@gmail.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1549,17 +1553,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Vit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ryanhan821@yahoo.com</t>
+          <t>annevit.av@icloud.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1571,19 +1575,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Uyen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Quinsay</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>r.quinsay@gmail.com</t>
-        </is>
-      </c>
+          <t>Diep</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1593,17 +1593,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Yong</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jiang</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jiangyong1998@hotmail.com</t>
+          <t>ryanhan821@yahoo.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1615,15 +1615,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Maliyah</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jeshani</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Quinsay</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>r.quinsay@gmail.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1633,17 +1637,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Xin</t>
+          <t>Yong</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deng</t>
+          <t>Jiang</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>cindydeng322@gmail.com</t>
+          <t>jiangyong1998@hotmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1655,19 +1659,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jeanette</t>
+          <t>Maliyah</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Perez</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>jeanetteperez72@gmail.com</t>
-        </is>
-      </c>
+          <t>Jeshani</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1677,15 +1677,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Xin</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Saad</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Deng</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>cindydeng322@gmail.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1695,17 +1699,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bibi</t>
+          <t>Jeanette</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Popovic</t>
+          <t>Perez</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>biba018@rogers.com</t>
+          <t>jeanetteperez72@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1717,19 +1721,15 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Haidan</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>haiden_wang@hotmail.ca</t>
-        </is>
-      </c>
+          <t>Saad</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1739,15 +1739,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Bibi</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hu</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Popovic</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>biba018@rogers.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1757,15 +1761,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Haidan</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rutter</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>haiden_wang@hotmail.ca</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1775,19 +1783,15 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>deanna</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>badovinac</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>dbadovinac@fibercast.com</t>
-        </is>
-      </c>
+          <t>Hu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1797,19 +1801,15 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vucic</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>kathy@parass.com</t>
-        </is>
-      </c>
+          <t>Rutter</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1819,17 +1819,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>deanna</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>badovinac</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>brucehankmoore@gmail.com</t>
+          <t>dbadovinac@fibercast.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gilligan</t>
+          <t>Vucic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kevin6862@hotmail.com</t>
+          <t>kathy@parass.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1863,17 +1863,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mary.kelly.remax@gmail.com</t>
+          <t>brucehankmoore@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1885,15 +1885,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rose</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Gilligan</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kevin6862@hotmail.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1903,17 +1907,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Nikola</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kvesic</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>knezic_zeljka@yahoo.com</t>
+          <t>mary.kelly.remax@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1925,19 +1929,15 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>steve</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>steve.wayne.kelly@gmail.com</t>
-        </is>
-      </c>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1947,15 +1947,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Baraa</t>
+          <t>Nikola</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Kvesic</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>knezic_zeljka@yahoo.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1965,15 +1969,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>steve</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Samuels</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>steve.wayne.kelly@gmail.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -1983,12 +1991,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nataly</t>
+          <t>Baraa</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -2001,12 +2009,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Ray</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Samuels</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -2019,19 +2027,15 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Nataly</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bantin</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>colincbantin@gmail.com</t>
-        </is>
-      </c>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2041,12 +2045,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Froats</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2059,17 +2063,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Bantin</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>larrymhenderson@gmail.com</t>
+          <t>colincbantin@gmail.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2081,19 +2085,15 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bonnie</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Modi</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>bonnie.modi@gmail.com</t>
-        </is>
-      </c>
+          <t>Froats</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2103,15 +2103,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ross</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Henderson</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>larrymhenderson@gmail.com</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2121,15 +2125,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Elliot</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Whittington</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Kuzmyn</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>rkuzmyn@gmail.com</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2139,15 +2147,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Bonnie</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Modi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>bonnie.modi@gmail.com</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2157,12 +2169,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Von Zuben</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2175,12 +2187,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Elliot</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Velanoff</t>
+          <t>Whittington</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2193,12 +2205,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Edlyn</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Von Zuben</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2211,19 +2223,15 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kijak</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>petey.kijak@gmail.com</t>
-        </is>
-      </c>
+          <t>Von Zuben</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2233,12 +2241,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sapra</t>
+          <t>Velanoff</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2251,19 +2259,15 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ella Rose</t>
+          <t>Edlyn</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ma</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>rmakrma@gmail.com</t>
-        </is>
-      </c>
+          <t>Ross</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2273,15 +2277,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jacqueline</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Kijak</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>petey.kijak@gmail.com</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2291,12 +2299,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Sapra</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2309,15 +2317,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>Ella Rose</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prendergast</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>rmakrma@gmail.com</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2327,12 +2339,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Jacqueline</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prendergast</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2345,19 +2357,15 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ponikvar</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>ponikvarsa@gmail.com</t>
-        </is>
-      </c>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2367,12 +2375,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Oren</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lasko</t>
+          <t>Prendergast</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2385,12 +2393,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Oshra</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lasko</t>
+          <t>Prendergast</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2403,17 +2411,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Flowers</t>
+          <t>ponikvar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jjflowers@hotmail.ca</t>
+          <t>ponikvarsa@gmail.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2425,19 +2433,15 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>antony</t>
+          <t>Oren</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>han</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>uw.antony@gmail.com</t>
-        </is>
-      </c>
+          <t>Lasko</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2447,12 +2451,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Antony</t>
+          <t>Oshra</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Lasko</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2465,15 +2469,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Haichen (Henry)</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Liu</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jjflowers@hotmail.ca</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2483,17 +2491,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Divya</t>
+          <t>antony</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kwatra</t>
+          <t>han</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>diiu@hotmail.com</t>
+          <t>uw.antony@gmail.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2505,19 +2513,15 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Antony</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>McMillan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>jackmcmi17@gmail.com</t>
-        </is>
-      </c>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2527,19 +2531,15 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Haichen (Henry)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Costa</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>fabian.pagani@icloud.com</t>
-        </is>
-      </c>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2549,17 +2549,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Melody</t>
+          <t>Divya</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Kwatra</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>melody2250hotmail@hotmail.com</t>
+          <t>diiu@hotmail.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2571,17 +2571,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>justin</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>bradt</t>
+          <t>McMillan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>justinbradt@gmail.com</t>
+          <t>jackmcmi17@gmail.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2593,15 +2593,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Quach</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>fabian.pagani@icloud.com</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2611,15 +2615,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Melody</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Griffith</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>melody2250hotmail@hotmail.com</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2629,17 +2637,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>justin</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>bradt</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>scrappiedoo10@hotmail.com</t>
+          <t>justinbradt@gmail.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2651,12 +2659,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Danny</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Han</t>
+          <t>Quach</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2669,12 +2677,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Gail</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deir</t>
+          <t>Griffith</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2687,17 +2695,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dhir</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kothari</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>mr.dhirkothari@gmail.com</t>
+          <t>scrappiedoo10@hotmail.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2709,19 +2717,15 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>morgan</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>brian.k.morgan@hotmail.com</t>
-        </is>
-      </c>
+          <t>Han</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2731,19 +2735,15 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>cvbaker@hotmail.com</t>
-        </is>
-      </c>
+          <t>Deir</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2753,17 +2753,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Dhir</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bobbitt</t>
+          <t>Kothari</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>amy.bobbitt@ig.ca</t>
+          <t>mr.dhirkothari@gmail.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2775,15 +2775,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Arvind</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kochar</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>morgan</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>brian.k.morgan@hotmail.com</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2793,17 +2797,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>pinto</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>leogbarone@icloud.com</t>
+          <t>cvbaker@hotmail.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2815,15 +2819,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Royan</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Bobbitt</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>amy.bobbitt@ig.ca</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2833,12 +2841,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Arhaan</t>
+          <t>Arvind</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jinnah</t>
+          <t>Kochar</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2851,15 +2859,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Arham</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jinnah</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>pinto</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>leogbarone@icloud.com</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2869,12 +2881,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hillmer</t>
+          <t>Royan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2887,12 +2899,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Arhaan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deary-Yu</t>
+          <t>Jinnah</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2905,12 +2917,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Arham</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Perevalova</t>
+          <t>Jinnah</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2923,7 +2935,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2941,19 +2953,15 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pitt</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>barbpitt21@gmail.com</t>
-        </is>
-      </c>
+          <t>Deary-Yu</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2963,19 +2971,15 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Defrang</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>rolanddefrang@icloud.com</t>
-        </is>
-      </c>
+          <t>Perevalova</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -2985,19 +2989,15 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Eunice</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dayrit</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>eunicereniel_d@yahoo.com</t>
-        </is>
-      </c>
+          <t>Hillmer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3007,15 +3007,19 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Eason</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Han</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>Pitt</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>barbpitt21@gmail.com</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3025,17 +3029,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Defrang</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>katwalker04@gmail.com</t>
+          <t>rolanddefrang@icloud.com</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3047,17 +3051,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Eunice</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Dayrit</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>walker.cm.jake@gmail.com</t>
+          <t>eunicereniel_d@yahoo.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3069,12 +3073,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Eason</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Han</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3087,15 +3091,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Heidi</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Plouffe</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>katwalker04@gmail.com</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3105,15 +3113,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Aimee</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Porter</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>walker.cm.jake@gmail.com</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3123,19 +3135,15 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Keyana</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Segato</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>kfsegato@icloud.com</t>
-        </is>
-      </c>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3145,19 +3153,15 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Seana</t>
+          <t>Heidi</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Maennling</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>seanamaennling@icloud.com</t>
-        </is>
-      </c>
+          <t>Plouffe</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3167,19 +3171,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mikaal</t>
+          <t>Aimee</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ansari</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>ansari.mikaal@gmail.com</t>
-        </is>
-      </c>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3189,17 +3189,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Aayan</t>
+          <t>Keyana</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>bonilla</t>
+          <t>Segato</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1bonillacaay@hdsb.ca</t>
+          <t>kfsegato@icloud.com</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3211,15 +3211,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Seana</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>Maennling</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>seanamaennling@icloud.com</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3229,17 +3233,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Donnelly</t>
+          <t>Awan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jdonnellybcba@gmail.com</t>
+          <t>mawan@stonebrooke.ca</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3251,17 +3255,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AUBREE</t>
+          <t>Jake Denver</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FRANCIS</t>
+          <t>Enriquez</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>aubsfrancis10@gmail.com</t>
+          <t>jake.business1017@outlook.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3273,15 +3277,19 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Brydon</t>
+          <t>Mikaal</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>Ansari</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ansari.mikaal@gmail.com</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3291,15 +3299,19 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fang</t>
+          <t>Aayan</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>bonilla</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>1bonillacaay@hdsb.ca</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3309,12 +3321,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Eddie</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3327,15 +3339,19 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Daren</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Zhang</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>Donnelly</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jdonnellybcba@gmail.com</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3345,15 +3361,19 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Aubree</t>
+          <t>AUBREE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Francis</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+          <t>FRANCIS</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>aubsfrancis10@gmail.com</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3363,19 +3383,15 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Stefano</t>
+          <t>Brydon</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Bomben</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>stefbomben@gmail.com</t>
-        </is>
-      </c>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3385,19 +3401,15 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>matthew</t>
+          <t>Fang</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>nesbitt</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>mnesbitt@cogeco.ca</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3407,19 +3419,15 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tania</t>
+          <t>Eddie</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>tani</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>ttani066@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3429,19 +3437,15 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Gloria</t>
+          <t>Daren</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tomlinson</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>gloria.tomlinson@gmail.com</t>
-        </is>
-      </c>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3451,19 +3455,15 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Parm</t>
+          <t>Aubree</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>parm76@hotmail.com</t>
-        </is>
-      </c>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3473,17 +3473,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Stefano</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bartlett</t>
+          <t>Bomben</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jdbartlett@gmail.com</t>
+          <t>stefbomben@gmail.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3495,17 +3495,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NOURA</t>
+          <t>matthew</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BALBAA</t>
+          <t>nesbitt</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>balbaanoura@gmail.com</t>
+          <t>mnesbitt@cogeco.ca</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3517,15 +3517,19 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Rene</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Quercia</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>Jeon</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>wjsaughks100@gmail.com</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3535,17 +3539,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>tania</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>McGuire</t>
+          <t>tani</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>mcguire11170@gmail.com</t>
+          <t>ttani066@gmail.com</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3557,17 +3561,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>jessica</t>
+          <t>Gloria</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>rickus</t>
+          <t>Tomlinson</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>jess.rickus@gmail.com</t>
+          <t>gloria.tomlinson@gmail.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3579,17 +3583,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Parm</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Armena</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>chrisarmena@gmail.com</t>
+          <t>parm76@hotmail.com</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3601,17 +3605,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Bartlett</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>riccimatthew95@gmail.com</t>
+          <t>jdbartlett@gmail.com</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3623,17 +3627,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>NOURA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Moazzam</t>
+          <t>BALBAA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>zara.moazzam.16@gmail.com</t>
+          <t>balbaanoura@gmail.com</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3645,19 +3649,15 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Lindsay</t>
+          <t>Rene</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Hooper</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>lindsayhooper79@gmail.com</t>
-        </is>
-      </c>
+          <t>Quercia</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3667,17 +3667,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CHANDRE</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MACDOUGALL</t>
+          <t>McGuire</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>chandre@gmail.com</t>
+          <t>mcguire11170@gmail.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3689,17 +3689,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>jessica</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Magagna</t>
+          <t>rickus</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>marina45@rogers.com</t>
+          <t>jess.rickus@gmail.com</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3711,17 +3711,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Lynda</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Armena</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>robandlyndawilson@gmail.com</t>
+          <t>chrisarmena@gmail.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3733,17 +3733,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Berfelz</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>bencoe01@hotmail.com</t>
+          <t>riccimatthew95@gmail.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3755,17 +3755,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Alpaugh</t>
+          <t>Moazzam</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>tlalpaugh@yahoo.ca</t>
+          <t>zara.moazzam.16@gmail.com</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3777,17 +3777,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Lindsay</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Snowden</t>
+          <t>Hooper</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>sydney.2205.ss@icloud.com</t>
+          <t>lindsayhooper79@gmail.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3799,17 +3799,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Juzar</t>
+          <t>CHANDRE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ebrahimjee</t>
+          <t>MACDOUGALL</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>juzzii@hotmail.com</t>
+          <t>chandre@gmail.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3821,17 +3821,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Magagna</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>mike_burgess78@hotmail.com</t>
+          <t>marina45@rogers.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3843,17 +3843,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>Lynda</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lu</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>pinglu224@hotmail.com</t>
+          <t>robandlyndawilson@gmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3865,17 +3865,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Berfelz</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>smartins2@cogeco.ca</t>
+          <t>bencoe01@hotmail.com</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3887,17 +3887,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Theresa</t>
+          <t>Tara</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Zamora</t>
+          <t>Alpaugh</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>theresazam1@gmail.com</t>
+          <t>tlalpaugh@yahoo.ca</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3909,17 +3909,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Yingmai</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Guo</t>
+          <t>Snowden</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>guoyingmai@gmail.com</t>
+          <t>sydney.2205.ss@icloud.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3931,15 +3931,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Juzar</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Chow</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>Ebrahimjee</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>juzzii@hotmail.com</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -3949,17 +3953,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>O'Loughlin</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>linda_olo@yahoo.ca</t>
+          <t>mike_burgess78@hotmail.com</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3971,17 +3975,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Gerry</t>
+          <t>Ping</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tessier</t>
+          <t>Lu</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>tessiergerry@gmail.com</t>
+          <t>pinglu224@hotmail.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3993,17 +3997,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>De Lucia</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>steve.delucia@ouitlook.com</t>
+          <t>smartins2@cogeco.ca</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4015,17 +4019,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>nick</t>
+          <t>Theresa</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>quartarone</t>
+          <t>Zamora</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>nickquartarone04@gmail.com</t>
+          <t>theresazam1@gmail.com</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4037,17 +4041,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Deliah</t>
+          <t>Yingmai</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>McLane</t>
+          <t>Guo</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>deliah.custodio@icloud.com</t>
+          <t>guoyingmai@gmail.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4059,12 +4063,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Qianying</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -4077,17 +4081,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sadi</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Arbid</t>
+          <t>O'Loughlin</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>arbid.arbid@hotmail.com</t>
+          <t>linda_olo@yahoo.ca</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4099,17 +4103,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Gerry</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jin</t>
+          <t>Tessier</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>xin_jin@hotmail.com</t>
+          <t>tessiergerry@gmail.com</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4121,17 +4125,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Harsh</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>De Lucia</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>harsh.canada2018@gmail.com</t>
+          <t>steve.delucia@ouitlook.com</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4143,17 +4147,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>nick</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>quartarone</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>tiger.liuy@gmail.com</t>
+          <t>nickquartarone04@gmail.com</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4165,17 +4169,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Jinhee</t>
+          <t>Deliah</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>McLane</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>kinikini0429@gmail.com</t>
+          <t>deliah.custodio@icloud.com</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4187,19 +4191,15 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RAIKO</t>
+          <t>Qianying</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LEE</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>raikolee@gmail.com</t>
-        </is>
-      </c>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -4209,17 +4209,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Sadi</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Lico</t>
+          <t>Arbid</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>jacobjlico@outlook.com</t>
+          <t>arbid.arbid@hotmail.com</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4231,17 +4231,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>nathalie</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>devault-arbid</t>
+          <t>Jin</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>devault.devault@hotmail.com</t>
+          <t>xin_jin@hotmail.com</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4253,17 +4253,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Harsh</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>alimiller314@gmail.com</t>
+          <t>harsh.canada2018@gmail.com</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4275,17 +4275,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Xie</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>cynthia.xie@gmail.com</t>
+          <t>tiger.liuy@gmail.com</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4297,17 +4297,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Jinhee</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Hedley</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>jeff74hedley@gmail.com</t>
+          <t>kinikini0429@gmail.com</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4319,17 +4319,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Crosby</t>
+          <t>RAIKO</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>crosby.gibson@rogers.com</t>
+          <t>raikolee@gmail.com</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4341,17 +4341,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Titei</t>
+          <t>Lico</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>temp.100@live.com</t>
+          <t>jacobjlico@outlook.com</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4363,17 +4363,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>nathalie</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>devault-arbid</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>tinarainbox@hotmail.com</t>
+          <t>devault.devault@hotmail.com</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4385,17 +4385,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Alison</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Marchese</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>marchese.ash@gmail.com</t>
+          <t>alimiller314@gmail.com</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4407,17 +4407,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Zamzam</t>
+          <t>Xie</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>omarrzamzam@gmail.com</t>
+          <t>cynthia.xie@gmail.com</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4429,17 +4429,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Yena</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Hedley</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ynhk1127@gmail.com</t>
+          <t>jeff74hedley@gmail.com</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4451,17 +4451,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Montalbano</t>
+          <t>Titei</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>amontalbano75@gmail.com</t>
+          <t>temp.100@live.com</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4473,17 +4473,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>luke.d.everest@gmail.com</t>
+          <t>tinarainbox@hotmail.com</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4495,17 +4495,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Tse</t>
+          <t>Marchese</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>nathantse@live.com</t>
+          <t>marchese.ash@gmail.com</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4517,17 +4517,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Farid</t>
+          <t>Zamzam</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>aawad62@gmail.com</t>
+          <t>omarrzamzam@gmail.com</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4539,17 +4539,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Yena</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Cox</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ethancox1337@gmail.com</t>
+          <t>ynhk1127@gmail.com</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4561,17 +4561,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Akl</t>
+          <t>Montalbano</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>mohamedakl99@gmail.com</t>
+          <t>amontalbano75@gmail.com</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4583,17 +4583,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ron</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>borbas</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ronborbas@gmail.com</t>
+          <t>luke.d.everest@gmail.com</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4605,17 +4605,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>katelyn</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>chung</t>
+          <t>Tse</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>katelynchung99@gmail.com</t>
+          <t>nathantse@live.com</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4627,17 +4627,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>Farid</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>wangkejuan@hotmail.com</t>
+          <t>aawad62@gmail.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4649,17 +4649,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Oana</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Titei</t>
+          <t>Cox</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>oana@titei.com</t>
+          <t>ethancox1337@gmail.com</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4671,17 +4671,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hyravy</t>
+          <t>Akl</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>nikkihyravy@gmail.com</t>
+          <t>mohamedakl99@gmail.com</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4693,17 +4693,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>jason</t>
+          <t>ron</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>borbas</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>jasonbear34@live.ca</t>
+          <t>ronborbas@gmail.com</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4715,17 +4715,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>jerry</t>
+          <t>katelyn</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>chung</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>jerry.hm@hotmail.com</t>
+          <t>katelynchung99@gmail.com</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4737,17 +4737,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Guillemette</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>rogerguillemette@yahoo.ca</t>
+          <t>wangkejuan@hotmail.com</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4759,17 +4759,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>bq</t>
+          <t>Oana</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>xu</t>
+          <t>Titei</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>mr.bq.xu@gmail.com</t>
+          <t>oana@titei.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4781,17 +4781,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>gallucci</t>
+          <t>Hyravy</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>j_delcol@yahoo.ca</t>
+          <t>nikkihyravy@gmail.com</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4803,17 +4803,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>jason</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>mh@intersurgical.ca</t>
+          <t>jasonbear34@live.ca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -4825,17 +4825,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>jerry</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Montalbano</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>linda@graffretail.com</t>
+          <t>jerry.hm@hotmail.com</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -4847,17 +4847,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>matheus</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>krumme</t>
+          <t>Guillemette</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>mjkrumme@gmail.com</t>
+          <t>rogerguillemette@yahoo.ca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -4869,17 +4869,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>bq</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t>xu</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>wangkejuan+@hotmail.com</t>
+          <t>mr.bq.xu@gmail.com</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -4891,17 +4891,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>alexander</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>chung</t>
+          <t>gallucci</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>alexanderchung88@gmail.com</t>
+          <t>j_delcol@yahoo.ca</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -4913,17 +4913,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>jamekoch9@gmail.com</t>
+          <t>mh@intersurgical.ca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4935,17 +4935,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>shuang</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>yao</t>
+          <t>Montalbano</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>stevenyaomolins@hotmail.com</t>
+          <t>linda@graffretail.com</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -4957,17 +4957,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Sherif</t>
+          <t>matheus</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Shama</t>
+          <t>krumme</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>sherifshama@me.com</t>
+          <t>mjkrumme@gmail.com</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -4979,17 +4979,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>El</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>amahalwy@gmail.com</t>
+          <t>wangkejuan+@hotmail.com</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5001,17 +5001,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>alexander</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Compas</t>
+          <t>chung</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>joshcompas@outlook.com</t>
+          <t>alexanderchung88@gmail.com</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5023,17 +5023,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>donna</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>petrarca</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>julesmom@hotmail.com</t>
+          <t>jamekoch9@gmail.com</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5045,17 +5045,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Elaine</t>
+          <t>shuang</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Boal</t>
+          <t>yao</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>eboal@bell.net</t>
+          <t>stevenyaomolins@hotmail.com</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5067,17 +5067,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Tara</t>
+          <t>Sherif</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Gasparik</t>
+          <t>Shama</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>tgasparik@cogeco.ca</t>
+          <t>sherifshama@me.com</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5089,17 +5089,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Hu</t>
+          <t>El</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>claudia.nrsg@gmail.com</t>
+          <t>amahalwy@gmail.com</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5111,17 +5111,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Lo</t>
+          <t>Compas</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>justinhllo10@gmail.com</t>
+          <t>joshcompas@outlook.com</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5133,17 +5133,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>donna</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Vander Velden</t>
+          <t>petrarca</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>stewvelden@gmail.com</t>
+          <t>julesmom@hotmail.com</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5155,17 +5155,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Elaine</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Sa</t>
+          <t>Boal</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>mohfouad01@gmail.com</t>
+          <t>eboal@bell.net</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5177,17 +5177,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Tara</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Ljubisic</t>
+          <t>Gasparik</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>rob.ljubisic@outlook.com</t>
+          <t>tgasparik@cogeco.ca</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5199,17 +5199,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Avni</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Dixit</t>
+          <t>Hu</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>avnidixit@gmail.com</t>
+          <t>claudia.nrsg@gmail.com</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5221,17 +5221,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Lo</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>peterandclare@gmail.com</t>
+          <t>justinhllo10@gmail.com</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5243,17 +5243,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Jowahir</t>
+          <t>Vander Velden</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>peter.jowahir@gmail.com</t>
+          <t>stewvelden@gmail.com</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5265,17 +5265,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Baldock</t>
+          <t>Sa</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>kbahula@hotmail.com</t>
+          <t>mohfouad01@gmail.com</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5287,17 +5287,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Jowahir</t>
+          <t>Ljubisic</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>jasmine.jowahir@gmail.com</t>
+          <t>rob.ljubisic@outlook.com</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5309,17 +5309,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Judi</t>
+          <t>Avni</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Laman</t>
+          <t>Dixit</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>judilynnv@hotmail.com</t>
+          <t>avnidixit@gmail.com</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5331,17 +5331,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Niya</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Jowahir</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>njowahir88@gmail.com</t>
+          <t>peterandclare@gmail.com</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5353,17 +5353,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tonogai</t>
+          <t>Jowahir</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>jtonogai@gmail.com</t>
+          <t>peter.jowahir@gmail.com</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5375,17 +5375,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Sebesta</t>
+          <t>Baldock</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>legsebesta@gmail.com</t>
+          <t>kbahula@hotmail.com</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5397,17 +5397,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Qian</t>
+          <t>Jowahir</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>yrqian@gmail.com</t>
+          <t>jasmine.jowahir@gmail.com</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5419,17 +5419,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Judi</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Laman</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>aomar6197@gmail.com</t>
+          <t>judilynnv@hotmail.com</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5441,17 +5441,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Dorthy</t>
+          <t>Niya</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Jowahir</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ddliu75@gmail.com</t>
+          <t>njowahir88@gmail.com</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5463,17 +5463,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Rev</t>
+          <t>Tonogai</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ryanrev86@gmail.com</t>
+          <t>jtonogai@gmail.com</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5485,17 +5485,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>maliya</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>holder</t>
+          <t>Sebesta</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>maliyaholder1587@gmail.com</t>
+          <t>legsebesta@gmail.com</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5507,17 +5507,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Sprah</t>
+          <t>Qian</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ktsprah@gmail.com</t>
+          <t>yrqian@gmail.com</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5529,17 +5529,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Sprah</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>tksprah@gmail.com</t>
+          <t>aomar6197@gmail.com</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5551,17 +5551,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>adam</t>
+          <t>Dorthy</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>quarrington</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>adamq1729@gmail.com</t>
+          <t>ddliu75@gmail.com</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5573,17 +5573,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Nerissa</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Bogdanis</t>
+          <t>Rev</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>nerissab1223@gmail.com</t>
+          <t>ryanrev86@gmail.com</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5595,17 +5595,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Teo</t>
+          <t>maliya</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Spady</t>
+          <t>holder</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>mspaady13@gmail.com</t>
+          <t>maliyaholder1587@gmail.com</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5617,17 +5617,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>LeeAnn</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Oleary</t>
+          <t>Sprah</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>leeannoleary3@gmail.com</t>
+          <t>ktsprah@gmail.com</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5639,17 +5639,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Bullock</t>
+          <t>Sprah</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>dwbulock1@gmail.com</t>
+          <t>tksprah@gmail.com</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5661,17 +5661,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>adam</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Rev</t>
+          <t>quarrington</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>krev@live.ca</t>
+          <t>adamq1729@gmail.com</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5683,17 +5683,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Mya</t>
+          <t>Nerissa</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Rinaldo</t>
+          <t>Bogdanis</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>mlr03@icloud.com</t>
+          <t>nerissab1223@gmail.com</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5705,17 +5705,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>GIRISH</t>
+          <t>Teo</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PURI</t>
+          <t>Spady</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>girishpuri15@gmail.com</t>
+          <t>mspaady13@gmail.com</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5727,17 +5727,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>LeeAnn</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Brankovic</t>
+          <t>Oleary</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>rebecca.brankovic8@gmail.com</t>
+          <t>leeannoleary3@gmail.com</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -5749,17 +5749,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Norene</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Bullock</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>jnmassey@bell.net</t>
+          <t>dwbulock1@gmail.com</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -5771,17 +5771,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Lydia</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Rev</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>lydialiu0110@gmail.com</t>
+          <t>krev@live.ca</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -5793,17 +5793,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Mackenzie</t>
+          <t>Mya</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Solomon</t>
+          <t>Rinaldo</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>mackenziesolomonn@gmail.com</t>
+          <t>mlr03@icloud.com</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -5815,17 +5815,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>GIRISH</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Hoover</t>
+          <t>PURI</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ashyhoovy@hotmail.com</t>
+          <t>girishpuri15@gmail.com</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -5837,17 +5837,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Solomon</t>
+          <t>Brankovic</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>nsolom4@uwo.ca</t>
+          <t>rebecca.brankovic8@gmail.com</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5859,17 +5859,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Madi</t>
+          <t>Norene</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Fulop</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>madisonfulop@yahoo.ca</t>
+          <t>jnmassey@bell.net</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -5881,17 +5881,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Lydia</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Liu</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>john.massey61@gmail.com</t>
+          <t>lydialiu0110@gmail.com</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5903,15 +5903,19 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Renee</t>
+          <t>Mackenzie</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ren</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
+          <t>Solomon</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>mackenziesolomonn@gmail.com</t>
+        </is>
+      </c>
       <c r="D261" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -5921,17 +5925,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Louis</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Marck</t>
+          <t>Hoover</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>louis@fermarltd.com</t>
+          <t>ashyhoovy@hotmail.com</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -5943,17 +5947,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>sean</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>oleary</t>
+          <t>Solomon</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>razorhosts@gmail.com</t>
+          <t>nsolom4@uwo.ca</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -5965,17 +5969,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Madi</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Fulop</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>goaliematty@gmail.com</t>
+          <t>madisonfulop@yahoo.ca</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -5987,17 +5991,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Lusk</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>owenlusk61@gmail.com</t>
+          <t>john.massey61@gmail.com</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6009,19 +6013,15 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Renee</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>aclayton711@gmail.com</t>
-        </is>
-      </c>
+          <t>Ren</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -6031,17 +6031,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>anne</t>
+          <t>Louis</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>leger-smith</t>
+          <t>Marck</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>anne.leger.smith@gmail.com</t>
+          <t>louis@fermarltd.com</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6053,17 +6053,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Rosanne</t>
+          <t>sean</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>oleary</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>rosannesells@gmail.com</t>
+          <t>razorhosts@gmail.com</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6075,17 +6075,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Lacroix</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>lacroix0155@gmail.com</t>
+          <t>goaliematty@gmail.com</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6097,17 +6097,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Duffield</t>
+          <t>Lusk</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>sduffield222@gmail.com</t>
+          <t>owenlusk61@gmail.com</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6119,17 +6119,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nawrot</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>russellnawrot@gmail.com</t>
+          <t>aclayton711@gmail.com</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6141,17 +6141,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>anne</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Andrews</t>
+          <t>leger-smith</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>kandrews141@gmail.com</t>
+          <t>anne.leger.smith@gmail.com</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6163,17 +6163,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Raymund</t>
+          <t>Rosanne</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Serina</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>raymundserina@gmail.com</t>
+          <t>rosannesells@gmail.com</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6185,17 +6185,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>cruz</t>
+          <t>Lacroix</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>davidbcruz@yahoo.com</t>
+          <t>lacroix0155@gmail.com</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6207,17 +6207,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Kym</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Singlehurst</t>
+          <t>Duffield</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>ksinglehurst@me.com</t>
+          <t>sduffield222@gmail.com</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6229,17 +6229,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Dela Vina</t>
+          <t>Nawrot</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>nancydelavina@gmail.com</t>
+          <t>russellnawrot@gmail.com</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6251,17 +6251,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Jonah</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Sy</t>
+          <t>Andrews</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>jsy@cocego.ca</t>
+          <t>kandrews141@gmail.com</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6273,17 +6273,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Raymund</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Dalusong</t>
+          <t>Serina</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>mariedalusong@gmail.com</t>
+          <t>raymundserina@gmail.com</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6295,17 +6295,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Ricky Dela Vina</t>
+          <t>cruz</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>n_dela_vina@yahoo.com</t>
+          <t>davidbcruz@yahoo.com</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6317,17 +6317,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Kym</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Xin</t>
+          <t>Singlehurst</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>xiangyanli@hotmail.com</t>
+          <t>ksinglehurst@me.com</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6339,17 +6339,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Arvin</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Dalusong</t>
+          <t>Dela Vina</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>arvincdal88@gmail.com</t>
+          <t>nancydelavina@gmail.com</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6361,17 +6361,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Romeo</t>
+          <t>Jonah</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Sy</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>cruzanova@gmail.com</t>
+          <t>jsy@cocego.ca</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6383,17 +6383,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Rodel</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Dalusong</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>rodmart65@gmail.com</t>
+          <t>mariedalusong@gmail.com</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6405,17 +6405,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Leigh</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Valiente</t>
+          <t>Ricky Dela Vina</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>leighvaliente@gmail.com</t>
+          <t>n_dela_vina@yahoo.com</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6427,17 +6427,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Cancino</t>
+          <t>Xin</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>fstcancino@yahoo.com</t>
+          <t>xiangyanli@hotmail.com</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6449,17 +6449,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Jerome</t>
+          <t>Arvin</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Magtibay</t>
+          <t>Dalusong</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>jcmagtibay@yahoo.com</t>
+          <t>arvincdal88@gmail.com</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6471,17 +6471,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Romeo</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Nassar</t>
+          <t>Cruz</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>nassarllc@gmail.com</t>
+          <t>cruzanova@gmail.com</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6493,17 +6493,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Sheila</t>
+          <t>Rodel</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Armena</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>sheila.armena@icloud.com</t>
+          <t>rodmart65@gmail.com</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6515,17 +6515,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ram</t>
+          <t>Leigh</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Bey</t>
+          <t>Valiente</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ramzi.beyh@gmail.com</t>
+          <t>leighvaliente@gmail.com</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6537,17 +6537,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Vien</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Bantog</t>
+          <t>Cancino</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>vsbantog@gmail.com</t>
+          <t>fstcancino@yahoo.com</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6559,17 +6559,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ricky</t>
+          <t>Jerome</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Dela Vina</t>
+          <t>Magtibay</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>megabites0113@gmail.com</t>
+          <t>jcmagtibay@yahoo.com</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6581,17 +6581,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Nassar</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>julia226688@gmail.com</t>
+          <t>nassarllc@gmail.com</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6603,17 +6603,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Xie</t>
+          <t>Armena</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>frankmxie@gmail.com</t>
+          <t>sheila.armena@icloud.com</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6625,17 +6625,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>samantha</t>
+          <t>Ram</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>wu</t>
+          <t>Bey</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>samantha.wu@tdsb.on.ca</t>
+          <t>ramzi.beyh@gmail.com</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6647,17 +6647,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Raj</t>
+          <t>Vien</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Pakan</t>
+          <t>Bantog</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>rajesh.pakan@gmail.com</t>
+          <t>vsbantog@gmail.com</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6669,17 +6669,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Ricky</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Defacendis</t>
+          <t>Dela Vina</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>defacendis@gmail.com</t>
+          <t>megabites0113@gmail.com</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6691,17 +6691,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>1397099@gmail.com</t>
+          <t>julia226688@gmail.com</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6713,7 +6713,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>tina.christina.xie@gmail.com</t>
+          <t>frankmxie@gmail.com</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6735,17 +6735,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Noreen</t>
+          <t>samantha</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Oldfield</t>
+          <t>wu</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>noreen.oldfield@hotmail.ca</t>
+          <t>samantha.wu@tdsb.on.ca</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -6757,17 +6757,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Xie</t>
+          <t>Pakan</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>anthonytxie@gmail.com</t>
+          <t>rajesh.pakan@gmail.com</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6779,15 +6779,19 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Turvey</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr"/>
+          <t>Defacendis</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>defacendis@gmail.com</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -6797,17 +6801,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Colin</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>cwang1780@gmail.com</t>
+          <t>1397099@gmail.com</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -6819,17 +6823,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>susan</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Zhao</t>
+          <t>Xie</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>zyy791115@hotmail.com</t>
+          <t>tina.christina.xie@gmail.com</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6841,17 +6845,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>Noreen</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Fu</t>
+          <t>Oldfield</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>jjjfff0418@gmail.com</t>
+          <t>noreen.oldfield@hotmail.ca</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6863,17 +6867,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Xie</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>nicholas.m.ng@gmail.com</t>
+          <t>anthonytxie@gmail.com</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -6893,11 +6897,7 @@
           <t>Turvey</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>andturvey@gmail.com</t>
-        </is>
-      </c>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
@@ -6907,17 +6907,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Huzaifa</t>
+          <t>Colin</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>isahuzaifam@gmail.com</t>
+          <t>cwang1780@gmail.com</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6929,17 +6929,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>susan</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Zhao</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>aaronwu751@gmail.com</t>
+          <t>zyy791115@hotmail.com</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6951,20 +6951,1716 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
+          <t>john</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Fu</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>jjjfff0418@gmail.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Ng</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>nicholas.m.ng@gmail.com</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Turvey</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>andturvey@gmail.com</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Huzaifa</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Mohamed</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>isahuzaifam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Wu</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>aaronwu751@gmail.com</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
           <t>Hellen</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>Dong</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
+      <c r="C314" t="inlineStr">
         <is>
           <t>hellen20230810@gmail.com</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Manuela</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Zapata</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>manuelazapata1999@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Healy</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>michael_paul_healy@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Ly</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>glorialy@sasktel.net</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Laurie</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Frnos</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>lauriedenos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Marisa</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>marisa.cpatel@gmail.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Stawarz</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>gethenrytofillhisemail@gmail.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Elaine</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Lauer</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>emlauer8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Gennady</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Philipchenko</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>gennady.ph@gmail.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Julie-Ann</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Tobien</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>jatobien@gmail.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Shauna</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Quarrington</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>sqathome1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>LaMaye</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>jlamaye77@gmail.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Sami</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Kuttab</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>sami.kuttab@gmail.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Barclay</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>jbarclay@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Raine</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Collier</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>rainecollier9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Viks</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Bahiya</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>vbahiya74@gmail.com</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Vandana</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Dahiya</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>vandanadahiya4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Gerry</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Champagne</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>gerry.champagne@innvesthotels.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Dam</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>loganjdam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Dennis</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Vitiello Family</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>jvitiello89@gmail.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Jaidon</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Gunn</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>jaidon14gunn@gmail.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Terrance</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Briffa</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>rita.briffa@innvesthotels.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Malik</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Khair</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>malik.khair@icloud.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Joe</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Vitiello</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>vytel1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Slade</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>joycetslade@gmail.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Jakob</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Rowley</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>jakejagger09@gmail.com</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Danison</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>keltrid1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Millard</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>llannmillard@gmail.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Himanshu</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Tanwar</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>himanshu_tanwaar90@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Solomon</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>solomonads@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Slade</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>willhslade@gmail.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Amia</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Fenyves</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Sousa</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>dianefreit@gmail.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Mireille</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Stettler</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>mirestettler@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Avry</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Fenyves</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Sliem</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Cheryl</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>McCrory</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>cmccrory@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Cortes</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>mcortes@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Solomon</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>asolomon@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Alarcon</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>aalarcon5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Gabor</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Fenyves</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>gfenyves@gmail.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Alniz</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Lallani</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>alnizlallani@gmail.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Starr</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>maidestarr@gmail.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Carlo</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Dava</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>carlodava@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Gladys</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Alarcon</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>gladysdelacruz@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Calvin</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Tiu</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>calvintiu@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Lambeck</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>chris_lambeck@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Joan</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Fox</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>joanfoxc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Arvin</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Dalusong</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>amdal88@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Basa</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>thebasafam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>1liupet.13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Bantog</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>gcbantog4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>zhang.aiden2015@gmail.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Langyu</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Zhou</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>langyuzhou08@gmail.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Cathy</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Gilligan</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>csgilligan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Leah</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Sy</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>leahsy@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Evan</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>zhang.evan2009@gmail.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Kristine</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Dava</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>kristinedava@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>PAUL</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>MCPARLAN</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>mcparlanp@gmail.com</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Donald</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>johnston.donald@gmail.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Giang</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Le</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>gianglh2013@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Beth</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Spigelman</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>bspigelman@gmail.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Morgan</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Barclay</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>mo23barclay@gmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>huali6718@gmail.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Zhao</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2011peter.zhao@gmail.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Carino</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>carino_john@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Vivian</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>1528044808@qq.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Maggie</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Wu</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>maggieying1218@gmail.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>chelsey</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>wang</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>chelsey.wang4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Kristian</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Gosling</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>goslingentertainment@gmail.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>winliuhouse@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>burloak@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Wei</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>An</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>cool.wei.cool@gmail.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
         <is>
           <t>burloak@pickleplex.ca</t>
         </is>
